--- a/data/simuladores/simulador-tarifarios-gas/tarifarios_gas_natural_Tiago_Felicia.xlsx
+++ b/data/simuladores/simulador-tarifarios-gas/tarifarios_gas_natural_Tiago_Felicia.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tiago\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B5F66CD-F00B-491D-869C-C8FBBF4EDA41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{475F71F8-5B44-4B18-96AD-91CBF36A1D0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tarifas_Gas_Master" sheetId="1" r:id="rId1"/>
@@ -192,9 +192,6 @@
     <t>EDPC_179</t>
   </si>
   <si>
-    <t>EDP - Gás Indexado</t>
-  </si>
-  <si>
     <t>EDPC_17</t>
   </si>
   <si>
@@ -222,9 +219,6 @@
     <t>https://poupaenergia.pt/</t>
   </si>
   <si>
-    <t>Endesa Gás Tarifa Indexada</t>
-  </si>
-  <si>
     <t>https://www.endesa.pt/particulares/planos/gas/indexada-gas</t>
   </si>
   <si>
@@ -249,51 +243,18 @@
     <t>https://www.galp.com/pt/energias/pt/combina</t>
   </si>
   <si>
-    <t>Galp | Casa &amp; Estrada (- 4% 1 energia s/DD)</t>
-  </si>
-  <si>
     <t>https://www.galp.com/pt/casa/planos-eletricidade-e-gas/casa-estrada</t>
   </si>
   <si>
-    <t>Galp | Casa &amp; Estrada (- 6% 1 energia c/DD ou 2 energias s/DD)</t>
-  </si>
-  <si>
-    <t>Galp | Casa &amp; Estrada (- 8% 2 energias c/DD)</t>
-  </si>
-  <si>
-    <t>Galp Plano Flexível - Gás</t>
-  </si>
-  <si>
     <t>https://casa.galp.pt/planos-eletricidade-e-gas/flexivel</t>
   </si>
   <si>
     <t>Goldenergy</t>
   </si>
   <si>
-    <t>Goldenergy - ACP</t>
-  </si>
-  <si>
     <t>https://goldenergy.pt/</t>
   </si>
   <si>
-    <t>Goldenergy  | Digital DD+FE</t>
-  </si>
-  <si>
-    <t>Goldenergy  | Digital DD ou FE</t>
-  </si>
-  <si>
-    <t>Goldenergy  | Digital</t>
-  </si>
-  <si>
-    <t>Goldenergy | Gold</t>
-  </si>
-  <si>
-    <t>Goldenergy | Desconto ao Máximo</t>
-  </si>
-  <si>
-    <t>Goldenergy Tarifa Index Gas 100% Online</t>
-  </si>
-  <si>
     <t>Iberdrola</t>
   </si>
   <si>
@@ -321,9 +282,6 @@
     <t>Luzigás</t>
   </si>
   <si>
-    <t>Luzigás - Plano Gás</t>
-  </si>
-  <si>
     <t>https://www.luzigas.pt/plano-gas/</t>
   </si>
   <si>
@@ -1101,13 +1059,55 @@
     <t>Endesa | Tarifa Aniversário Gás · (Depois dos 3 meses iniciais)</t>
   </si>
   <si>
-    <t>G9 | Vantagem+| FE</t>
-  </si>
-  <si>
     <t>Plenitude | Tarifa Fácil Plus Gás - Há Cheque Amazon 30€</t>
   </si>
   <si>
     <t>Plenitude |Tarifa TS Fácil Plus Gás</t>
+  </si>
+  <si>
+    <t>Luzigás | Plano Gás</t>
+  </si>
+  <si>
+    <t>Goldenergy | ACP Gás</t>
+  </si>
+  <si>
+    <t>Goldenergy | Tarifa Index Gas 100% Online</t>
+  </si>
+  <si>
+    <t>EDP | Indexado | Gás</t>
+  </si>
+  <si>
+    <t>Galp | Plano Flexível | Gás</t>
+  </si>
+  <si>
+    <t>Endesa | Tarifa Indexada | Gás</t>
+  </si>
+  <si>
+    <t>G9 | Energia +| Gás | FE</t>
+  </si>
+  <si>
+    <t>Galp | Casa &amp; Estrada |Gás | (- 4% 1 energia s/DD)</t>
+  </si>
+  <si>
+    <t>Galp | Casa &amp; Estrada |Gás | (- 6% 1 energia c/DD ou 2 energias s/DD)</t>
+  </si>
+  <si>
+    <t>Galp | Casa &amp; Estrada |Gás | (- 8% 2 energias c/DD)</t>
+  </si>
+  <si>
+    <t>Goldenergy  | Digital | Gás | DD+FE</t>
+  </si>
+  <si>
+    <t>Goldenergy  | Digital | Gás | DD ou FE</t>
+  </si>
+  <si>
+    <t>Goldenergy  | Digital | Gás</t>
+  </si>
+  <si>
+    <t>Goldenergy | Gold | Gás</t>
+  </si>
+  <si>
+    <t>Goldenergy | Desconto ao Máximo | Gás</t>
   </si>
 </sst>
 </file>
@@ -1596,13 +1596,13 @@
         <v>16</v>
       </c>
       <c r="R1" t="s">
-        <v>343</v>
+        <v>329</v>
       </c>
       <c r="S1" t="s">
-        <v>335</v>
+        <v>321</v>
       </c>
       <c r="T1" t="s">
-        <v>336</v>
+        <v>322</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
@@ -3170,13 +3170,13 @@
         <v>43</v>
       </c>
       <c r="B38" t="s">
+        <v>345</v>
+      </c>
+      <c r="C38" t="s">
         <v>51</v>
       </c>
-      <c r="C38" t="s">
+      <c r="D38" t="s">
         <v>52</v>
-      </c>
-      <c r="D38" t="s">
-        <v>53</v>
       </c>
       <c r="E38" t="s">
         <v>20</v>
@@ -3197,16 +3197,16 @@
         <v>7.2900000000000006E-2</v>
       </c>
       <c r="K38" t="s">
+        <v>53</v>
+      </c>
+      <c r="L38" t="s">
+        <v>24</v>
+      </c>
+      <c r="M38" t="s">
         <v>54</v>
       </c>
-      <c r="L38" t="s">
-        <v>24</v>
-      </c>
-      <c r="M38" t="s">
+      <c r="P38" t="s">
         <v>55</v>
-      </c>
-      <c r="P38" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.25">
@@ -3214,13 +3214,13 @@
         <v>43</v>
       </c>
       <c r="B39" t="s">
+        <v>345</v>
+      </c>
+      <c r="C39" t="s">
         <v>51</v>
       </c>
-      <c r="C39" t="s">
+      <c r="D39" t="s">
         <v>52</v>
-      </c>
-      <c r="D39" t="s">
-        <v>53</v>
       </c>
       <c r="E39" t="s">
         <v>20</v>
@@ -3241,16 +3241,16 @@
         <v>0.107</v>
       </c>
       <c r="K39" t="s">
+        <v>53</v>
+      </c>
+      <c r="L39" t="s">
+        <v>24</v>
+      </c>
+      <c r="M39" t="s">
         <v>54</v>
       </c>
-      <c r="L39" t="s">
-        <v>24</v>
-      </c>
-      <c r="M39" t="s">
+      <c r="P39" t="s">
         <v>55</v>
-      </c>
-      <c r="P39" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.25">
@@ -3258,13 +3258,13 @@
         <v>43</v>
       </c>
       <c r="B40" t="s">
+        <v>345</v>
+      </c>
+      <c r="C40" t="s">
         <v>51</v>
       </c>
-      <c r="C40" t="s">
+      <c r="D40" t="s">
         <v>52</v>
-      </c>
-      <c r="D40" t="s">
-        <v>53</v>
       </c>
       <c r="E40" t="s">
         <v>20</v>
@@ -3285,16 +3285,16 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="K40" t="s">
+        <v>53</v>
+      </c>
+      <c r="L40" t="s">
+        <v>24</v>
+      </c>
+      <c r="M40" t="s">
         <v>54</v>
       </c>
-      <c r="L40" t="s">
-        <v>24</v>
-      </c>
-      <c r="M40" t="s">
+      <c r="P40" t="s">
         <v>55</v>
-      </c>
-      <c r="P40" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.25">
@@ -3302,13 +3302,13 @@
         <v>43</v>
       </c>
       <c r="B41" t="s">
+        <v>345</v>
+      </c>
+      <c r="C41" t="s">
         <v>51</v>
       </c>
-      <c r="C41" t="s">
+      <c r="D41" t="s">
         <v>52</v>
-      </c>
-      <c r="D41" t="s">
-        <v>53</v>
       </c>
       <c r="E41" t="s">
         <v>20</v>
@@ -3329,24 +3329,24 @@
         <v>0.19370000000000001</v>
       </c>
       <c r="K41" t="s">
+        <v>53</v>
+      </c>
+      <c r="L41" t="s">
+        <v>24</v>
+      </c>
+      <c r="M41" t="s">
         <v>54</v>
       </c>
-      <c r="L41" t="s">
-        <v>24</v>
-      </c>
-      <c r="M41" t="s">
+      <c r="P41" t="s">
         <v>55</v>
-      </c>
-      <c r="P41" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B42" t="s">
-        <v>348</v>
+        <v>334</v>
       </c>
       <c r="D42" t="s">
         <v>19</v>
@@ -3379,24 +3379,24 @@
         <v>24</v>
       </c>
       <c r="P42" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q42" t="s">
-        <v>344</v>
+        <v>330</v>
       </c>
       <c r="R42">
         <v>3</v>
       </c>
       <c r="S42" t="s">
-        <v>337</v>
+        <v>323</v>
       </c>
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B43" t="s">
-        <v>348</v>
+        <v>334</v>
       </c>
       <c r="D43" t="s">
         <v>19</v>
@@ -3429,24 +3429,24 @@
         <v>24</v>
       </c>
       <c r="P43" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q43" t="s">
-        <v>344</v>
+        <v>330</v>
       </c>
       <c r="R43">
         <v>3</v>
       </c>
       <c r="S43" t="s">
-        <v>337</v>
+        <v>323</v>
       </c>
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B44" t="s">
-        <v>348</v>
+        <v>334</v>
       </c>
       <c r="D44" t="s">
         <v>19</v>
@@ -3479,24 +3479,24 @@
         <v>24</v>
       </c>
       <c r="P44" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q44" t="s">
-        <v>344</v>
+        <v>330</v>
       </c>
       <c r="R44">
         <v>3</v>
       </c>
       <c r="S44" t="s">
-        <v>337</v>
+        <v>323</v>
       </c>
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B45" t="s">
-        <v>348</v>
+        <v>334</v>
       </c>
       <c r="D45" t="s">
         <v>19</v>
@@ -3529,24 +3529,24 @@
         <v>24</v>
       </c>
       <c r="P45" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q45" t="s">
-        <v>344</v>
+        <v>330</v>
       </c>
       <c r="R45">
         <v>3</v>
       </c>
       <c r="S45" t="s">
-        <v>337</v>
+        <v>323</v>
       </c>
     </row>
     <row r="46" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B46" t="s">
-        <v>337</v>
+        <v>323</v>
       </c>
       <c r="D46" t="s">
         <v>19</v>
@@ -3579,10 +3579,10 @@
         <v>24</v>
       </c>
       <c r="P46" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q46" t="s">
-        <v>345</v>
+        <v>331</v>
       </c>
       <c r="T46">
         <v>1</v>
@@ -3590,10 +3590,10 @@
     </row>
     <row r="47" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B47" t="s">
-        <v>337</v>
+        <v>323</v>
       </c>
       <c r="D47" t="s">
         <v>19</v>
@@ -3626,10 +3626,10 @@
         <v>24</v>
       </c>
       <c r="P47" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q47" t="s">
-        <v>345</v>
+        <v>331</v>
       </c>
       <c r="T47">
         <v>1</v>
@@ -3637,10 +3637,10 @@
     </row>
     <row r="48" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B48" t="s">
-        <v>337</v>
+        <v>323</v>
       </c>
       <c r="D48" t="s">
         <v>19</v>
@@ -3673,10 +3673,10 @@
         <v>24</v>
       </c>
       <c r="P48" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q48" t="s">
-        <v>345</v>
+        <v>331</v>
       </c>
       <c r="T48">
         <v>1</v>
@@ -3684,10 +3684,10 @@
     </row>
     <row r="49" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B49" t="s">
-        <v>337</v>
+        <v>323</v>
       </c>
       <c r="D49" t="s">
         <v>19</v>
@@ -3720,10 +3720,10 @@
         <v>24</v>
       </c>
       <c r="P49" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q49" t="s">
-        <v>345</v>
+        <v>331</v>
       </c>
       <c r="T49">
         <v>1</v>
@@ -3731,10 +3731,10 @@
     </row>
     <row r="50" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B50" t="s">
-        <v>338</v>
+        <v>324</v>
       </c>
       <c r="D50" t="s">
         <v>19</v>
@@ -3773,24 +3773,24 @@
         <v>4</v>
       </c>
       <c r="P50" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="Q50" t="s">
-        <v>346</v>
+        <v>332</v>
       </c>
       <c r="R50">
         <v>3</v>
       </c>
       <c r="S50" t="s">
-        <v>341</v>
+        <v>327</v>
       </c>
     </row>
     <row r="51" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B51" t="s">
-        <v>338</v>
+        <v>324</v>
       </c>
       <c r="D51" t="s">
         <v>19</v>
@@ -3829,24 +3829,24 @@
         <v>4</v>
       </c>
       <c r="P51" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="Q51" t="s">
-        <v>346</v>
+        <v>332</v>
       </c>
       <c r="R51">
         <v>3</v>
       </c>
       <c r="S51" t="s">
-        <v>341</v>
+        <v>327</v>
       </c>
     </row>
     <row r="52" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B52" t="s">
-        <v>338</v>
+        <v>324</v>
       </c>
       <c r="D52" t="s">
         <v>19</v>
@@ -3885,24 +3885,24 @@
         <v>4</v>
       </c>
       <c r="P52" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="Q52" t="s">
-        <v>346</v>
+        <v>332</v>
       </c>
       <c r="R52">
         <v>3</v>
       </c>
       <c r="S52" t="s">
-        <v>341</v>
+        <v>327</v>
       </c>
     </row>
     <row r="53" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B53" t="s">
-        <v>338</v>
+        <v>324</v>
       </c>
       <c r="D53" t="s">
         <v>19</v>
@@ -3941,24 +3941,24 @@
         <v>4</v>
       </c>
       <c r="P53" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="Q53" t="s">
-        <v>346</v>
+        <v>332</v>
       </c>
       <c r="R53">
         <v>3</v>
       </c>
       <c r="S53" t="s">
-        <v>341</v>
+        <v>327</v>
       </c>
     </row>
     <row r="54" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B54" t="s">
-        <v>339</v>
+        <v>325</v>
       </c>
       <c r="D54" t="s">
         <v>19</v>
@@ -3997,24 +3997,24 @@
         <v>4</v>
       </c>
       <c r="P54" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="Q54" t="s">
-        <v>347</v>
+        <v>333</v>
       </c>
       <c r="R54">
         <v>3</v>
       </c>
       <c r="S54" t="s">
-        <v>340</v>
+        <v>326</v>
       </c>
     </row>
     <row r="55" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>339</v>
+        <v>325</v>
       </c>
       <c r="D55" t="s">
         <v>19</v>
@@ -4053,24 +4053,24 @@
         <v>4</v>
       </c>
       <c r="P55" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="Q55" t="s">
-        <v>347</v>
+        <v>333</v>
       </c>
       <c r="R55">
         <v>3</v>
       </c>
       <c r="S55" t="s">
-        <v>340</v>
+        <v>326</v>
       </c>
     </row>
     <row r="56" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B56" t="s">
-        <v>339</v>
+        <v>325</v>
       </c>
       <c r="D56" t="s">
         <v>19</v>
@@ -4109,24 +4109,24 @@
         <v>4</v>
       </c>
       <c r="P56" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="Q56" t="s">
-        <v>347</v>
+        <v>333</v>
       </c>
       <c r="R56">
         <v>3</v>
       </c>
       <c r="S56" t="s">
-        <v>340</v>
+        <v>326</v>
       </c>
     </row>
     <row r="57" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>339</v>
+        <v>325</v>
       </c>
       <c r="D57" t="s">
         <v>19</v>
@@ -4165,24 +4165,24 @@
         <v>4</v>
       </c>
       <c r="P57" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="Q57" t="s">
-        <v>347</v>
+        <v>333</v>
       </c>
       <c r="R57">
         <v>3</v>
       </c>
       <c r="S57" t="s">
-        <v>340</v>
+        <v>326</v>
       </c>
     </row>
     <row r="58" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>341</v>
+        <v>327</v>
       </c>
       <c r="D58" t="s">
         <v>19</v>
@@ -4215,10 +4215,10 @@
         <v>24</v>
       </c>
       <c r="P58" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="Q58" t="s">
-        <v>351</v>
+        <v>337</v>
       </c>
       <c r="T58">
         <v>1</v>
@@ -4226,10 +4226,10 @@
     </row>
     <row r="59" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B59" t="s">
-        <v>341</v>
+        <v>327</v>
       </c>
       <c r="D59" t="s">
         <v>19</v>
@@ -4262,10 +4262,10 @@
         <v>24</v>
       </c>
       <c r="P59" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="Q59" t="s">
-        <v>351</v>
+        <v>337</v>
       </c>
       <c r="T59">
         <v>1</v>
@@ -4273,10 +4273,10 @@
     </row>
     <row r="60" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B60" t="s">
-        <v>341</v>
+        <v>327</v>
       </c>
       <c r="D60" t="s">
         <v>19</v>
@@ -4309,10 +4309,10 @@
         <v>24</v>
       </c>
       <c r="P60" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="Q60" t="s">
-        <v>351</v>
+        <v>337</v>
       </c>
       <c r="T60">
         <v>1</v>
@@ -4320,10 +4320,10 @@
     </row>
     <row r="61" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B61" t="s">
-        <v>341</v>
+        <v>327</v>
       </c>
       <c r="D61" t="s">
         <v>19</v>
@@ -4356,10 +4356,10 @@
         <v>24</v>
       </c>
       <c r="P61" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="Q61" t="s">
-        <v>351</v>
+        <v>337</v>
       </c>
       <c r="T61">
         <v>1</v>
@@ -4367,10 +4367,10 @@
     </row>
     <row r="62" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B62" t="s">
-        <v>340</v>
+        <v>326</v>
       </c>
       <c r="D62" t="s">
         <v>19</v>
@@ -4403,10 +4403,10 @@
         <v>24</v>
       </c>
       <c r="P62" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="Q62" t="s">
-        <v>350</v>
+        <v>336</v>
       </c>
       <c r="T62">
         <v>1</v>
@@ -4414,10 +4414,10 @@
     </row>
     <row r="63" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B63" t="s">
-        <v>340</v>
+        <v>326</v>
       </c>
       <c r="D63" t="s">
         <v>19</v>
@@ -4450,10 +4450,10 @@
         <v>24</v>
       </c>
       <c r="P63" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="Q63" t="s">
-        <v>350</v>
+        <v>336</v>
       </c>
       <c r="T63">
         <v>1</v>
@@ -4461,10 +4461,10 @@
     </row>
     <row r="64" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B64" t="s">
-        <v>340</v>
+        <v>326</v>
       </c>
       <c r="D64" t="s">
         <v>19</v>
@@ -4497,10 +4497,10 @@
         <v>24</v>
       </c>
       <c r="P64" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="Q64" t="s">
-        <v>350</v>
+        <v>336</v>
       </c>
       <c r="T64">
         <v>1</v>
@@ -4508,10 +4508,10 @@
     </row>
     <row r="65" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B65" t="s">
-        <v>340</v>
+        <v>326</v>
       </c>
       <c r="D65" t="s">
         <v>19</v>
@@ -4544,10 +4544,10 @@
         <v>24</v>
       </c>
       <c r="P65" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="Q65" t="s">
-        <v>350</v>
+        <v>336</v>
       </c>
       <c r="T65">
         <v>1</v>
@@ -4555,10 +4555,10 @@
     </row>
     <row r="66" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B66" t="s">
-        <v>349</v>
+        <v>335</v>
       </c>
       <c r="D66" t="s">
         <v>19</v>
@@ -4591,21 +4591,21 @@
         <v>24</v>
       </c>
       <c r="P66" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="R66">
         <v>3</v>
       </c>
       <c r="S66" t="s">
-        <v>342</v>
+        <v>328</v>
       </c>
     </row>
     <row r="67" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B67" t="s">
-        <v>349</v>
+        <v>335</v>
       </c>
       <c r="D67" t="s">
         <v>19</v>
@@ -4638,21 +4638,21 @@
         <v>24</v>
       </c>
       <c r="P67" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="R67">
         <v>3</v>
       </c>
       <c r="S67" t="s">
-        <v>342</v>
+        <v>328</v>
       </c>
     </row>
     <row r="68" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B68" t="s">
-        <v>342</v>
+        <v>328</v>
       </c>
       <c r="D68" t="s">
         <v>19</v>
@@ -4685,7 +4685,7 @@
         <v>24</v>
       </c>
       <c r="P68" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T68">
         <v>1</v>
@@ -4693,10 +4693,10 @@
     </row>
     <row r="69" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B69" t="s">
-        <v>342</v>
+        <v>328</v>
       </c>
       <c r="D69" t="s">
         <v>19</v>
@@ -4729,7 +4729,7 @@
         <v>24</v>
       </c>
       <c r="P69" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T69">
         <v>1</v>
@@ -4737,13 +4737,13 @@
     </row>
     <row r="70" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B70" t="s">
-        <v>61</v>
+        <v>347</v>
       </c>
       <c r="D70" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E70" t="s">
         <v>20</v>
@@ -4764,7 +4764,7 @@
         <v>0.15135299999999999</v>
       </c>
       <c r="K70" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="L70" t="s">
         <v>24</v>
@@ -4773,18 +4773,18 @@
         <v>24</v>
       </c>
       <c r="P70" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="71" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B71" t="s">
-        <v>61</v>
+        <v>347</v>
       </c>
       <c r="D71" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E71" t="s">
         <v>20</v>
@@ -4805,7 +4805,7 @@
         <v>0.18545300000000001</v>
       </c>
       <c r="K71" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="L71" t="s">
         <v>24</v>
@@ -4814,18 +4814,18 @@
         <v>24</v>
       </c>
       <c r="P71" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="72" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B72" t="s">
-        <v>61</v>
+        <v>347</v>
       </c>
       <c r="D72" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E72" t="s">
         <v>20</v>
@@ -4846,7 +4846,7 @@
         <v>0.21845300000000001</v>
       </c>
       <c r="K72" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="L72" t="s">
         <v>24</v>
@@ -4855,18 +4855,18 @@
         <v>24</v>
       </c>
       <c r="P72" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="73" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B73" t="s">
-        <v>61</v>
+        <v>347</v>
       </c>
       <c r="D73" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E73" t="s">
         <v>20</v>
@@ -4887,7 +4887,7 @@
         <v>0.27215299999999998</v>
       </c>
       <c r="K73" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="L73" t="s">
         <v>24</v>
@@ -4896,15 +4896,15 @@
         <v>24</v>
       </c>
       <c r="P73" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="74" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B74" t="s">
-        <v>352</v>
+        <v>338</v>
       </c>
       <c r="D74" t="s">
         <v>19</v>
@@ -4937,21 +4937,21 @@
         <v>24</v>
       </c>
       <c r="P74" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="R74">
         <v>3</v>
       </c>
       <c r="S74" t="s">
-        <v>353</v>
+        <v>339</v>
       </c>
     </row>
     <row r="75" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B75" t="s">
-        <v>352</v>
+        <v>338</v>
       </c>
       <c r="D75" t="s">
         <v>19</v>
@@ -4984,21 +4984,21 @@
         <v>24</v>
       </c>
       <c r="P75" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="R75">
         <v>3</v>
       </c>
       <c r="S75" t="s">
-        <v>353</v>
+        <v>339</v>
       </c>
     </row>
     <row r="76" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B76" t="s">
-        <v>352</v>
+        <v>338</v>
       </c>
       <c r="D76" t="s">
         <v>19</v>
@@ -5031,21 +5031,21 @@
         <v>24</v>
       </c>
       <c r="P76" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="R76">
         <v>3</v>
       </c>
       <c r="S76" t="s">
-        <v>353</v>
+        <v>339</v>
       </c>
     </row>
     <row r="77" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B77" t="s">
-        <v>352</v>
+        <v>338</v>
       </c>
       <c r="D77" t="s">
         <v>19</v>
@@ -5078,21 +5078,21 @@
         <v>24</v>
       </c>
       <c r="P77" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77" t="s">
-        <v>353</v>
+        <v>339</v>
       </c>
     </row>
     <row r="78" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B78" t="s">
-        <v>353</v>
+        <v>339</v>
       </c>
       <c r="D78" t="s">
         <v>19</v>
@@ -5125,7 +5125,7 @@
         <v>24</v>
       </c>
       <c r="P78" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="T78">
         <v>1</v>
@@ -5133,10 +5133,10 @@
     </row>
     <row r="79" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B79" t="s">
-        <v>353</v>
+        <v>339</v>
       </c>
       <c r="D79" t="s">
         <v>19</v>
@@ -5169,7 +5169,7 @@
         <v>24</v>
       </c>
       <c r="P79" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="T79">
         <v>1</v>
@@ -5177,10 +5177,10 @@
     </row>
     <row r="80" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B80" t="s">
-        <v>353</v>
+        <v>339</v>
       </c>
       <c r="D80" t="s">
         <v>19</v>
@@ -5213,7 +5213,7 @@
         <v>24</v>
       </c>
       <c r="P80" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="T80">
         <v>1</v>
@@ -5221,10 +5221,10 @@
     </row>
     <row r="81" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B81" t="s">
-        <v>353</v>
+        <v>339</v>
       </c>
       <c r="D81" t="s">
         <v>19</v>
@@ -5257,7 +5257,7 @@
         <v>24</v>
       </c>
       <c r="P81" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="T81">
         <v>1</v>
@@ -5265,10 +5265,10 @@
     </row>
     <row r="82" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B82" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="D82" t="s">
         <v>19</v>
@@ -5304,18 +5304,18 @@
         <v>3</v>
       </c>
       <c r="P82" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="Q82" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="83" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B83" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="D83" t="s">
         <v>19</v>
@@ -5351,18 +5351,18 @@
         <v>3</v>
       </c>
       <c r="P83" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="Q83" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="84" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B84" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="D84" t="s">
         <v>19</v>
@@ -5398,18 +5398,18 @@
         <v>3</v>
       </c>
       <c r="P84" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="Q84" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="85" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B85" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="D85" t="s">
         <v>19</v>
@@ -5445,18 +5445,18 @@
         <v>3</v>
       </c>
       <c r="P85" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="Q85" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="86" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B86" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D86" t="s">
         <v>19</v>
@@ -5489,15 +5489,15 @@
         <v>24</v>
       </c>
       <c r="P86" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="87" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B87" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D87" t="s">
         <v>19</v>
@@ -5530,15 +5530,15 @@
         <v>24</v>
       </c>
       <c r="P87" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="88" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B88" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D88" t="s">
         <v>19</v>
@@ -5571,15 +5571,15 @@
         <v>24</v>
       </c>
       <c r="P88" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="89" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B89" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D89" t="s">
         <v>19</v>
@@ -5612,15 +5612,15 @@
         <v>24</v>
       </c>
       <c r="P89" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="90" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>70</v>
+        <v>349</v>
       </c>
       <c r="D90" t="s">
         <v>19</v>
@@ -5653,15 +5653,15 @@
         <v>24</v>
       </c>
       <c r="P90" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="91" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>70</v>
+        <v>349</v>
       </c>
       <c r="D91" t="s">
         <v>19</v>
@@ -5694,15 +5694,15 @@
         <v>24</v>
       </c>
       <c r="P91" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="92" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>70</v>
+        <v>349</v>
       </c>
       <c r="D92" t="s">
         <v>19</v>
@@ -5735,15 +5735,15 @@
         <v>24</v>
       </c>
       <c r="P92" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="93" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>70</v>
+        <v>349</v>
       </c>
       <c r="D93" t="s">
         <v>19</v>
@@ -5776,15 +5776,15 @@
         <v>24</v>
       </c>
       <c r="P93" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="94" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B94" t="s">
-        <v>72</v>
+        <v>350</v>
       </c>
       <c r="D94" t="s">
         <v>19</v>
@@ -5817,15 +5817,15 @@
         <v>24</v>
       </c>
       <c r="P94" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="95" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B95" t="s">
-        <v>72</v>
+        <v>350</v>
       </c>
       <c r="D95" t="s">
         <v>19</v>
@@ -5858,15 +5858,15 @@
         <v>24</v>
       </c>
       <c r="P95" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="96" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B96" t="s">
-        <v>72</v>
+        <v>350</v>
       </c>
       <c r="D96" t="s">
         <v>19</v>
@@ -5899,15 +5899,15 @@
         <v>24</v>
       </c>
       <c r="P96" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="97" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B97" t="s">
-        <v>72</v>
+        <v>350</v>
       </c>
       <c r="D97" t="s">
         <v>19</v>
@@ -5940,15 +5940,15 @@
         <v>24</v>
       </c>
       <c r="P97" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="98" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B98" t="s">
-        <v>73</v>
+        <v>351</v>
       </c>
       <c r="D98" t="s">
         <v>19</v>
@@ -5981,15 +5981,15 @@
         <v>24</v>
       </c>
       <c r="P98" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="99" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B99" t="s">
-        <v>73</v>
+        <v>351</v>
       </c>
       <c r="D99" t="s">
         <v>19</v>
@@ -6022,15 +6022,15 @@
         <v>24</v>
       </c>
       <c r="P99" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="100" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B100" t="s">
-        <v>73</v>
+        <v>351</v>
       </c>
       <c r="D100" t="s">
         <v>19</v>
@@ -6063,15 +6063,15 @@
         <v>24</v>
       </c>
       <c r="P100" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="101" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B101" t="s">
-        <v>73</v>
+        <v>351</v>
       </c>
       <c r="D101" t="s">
         <v>19</v>
@@ -6104,18 +6104,18 @@
         <v>24</v>
       </c>
       <c r="P101" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="102" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B102" t="s">
-        <v>74</v>
+        <v>346</v>
       </c>
       <c r="D102" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E102" t="s">
         <v>20</v>
@@ -6136,27 +6136,27 @@
         <v>7.9899999999999999E-2</v>
       </c>
       <c r="K102" t="s">
+        <v>53</v>
+      </c>
+      <c r="L102" t="s">
+        <v>24</v>
+      </c>
+      <c r="M102" t="s">
         <v>54</v>
       </c>
-      <c r="L102" t="s">
-        <v>24</v>
-      </c>
-      <c r="M102" t="s">
-        <v>55</v>
-      </c>
       <c r="P102" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
     </row>
     <row r="103" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B103" t="s">
-        <v>74</v>
+        <v>346</v>
       </c>
       <c r="D103" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E103" t="s">
         <v>20</v>
@@ -6177,27 +6177,27 @@
         <v>0.14460000000000001</v>
       </c>
       <c r="K103" t="s">
+        <v>53</v>
+      </c>
+      <c r="L103" t="s">
+        <v>24</v>
+      </c>
+      <c r="M103" t="s">
         <v>54</v>
       </c>
-      <c r="L103" t="s">
-        <v>24</v>
-      </c>
-      <c r="M103" t="s">
-        <v>55</v>
-      </c>
       <c r="P103" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
     </row>
     <row r="104" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B104" t="s">
-        <v>74</v>
+        <v>346</v>
       </c>
       <c r="D104" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E104" t="s">
         <v>20</v>
@@ -6218,27 +6218,27 @@
         <v>0.2072</v>
       </c>
       <c r="K104" t="s">
+        <v>53</v>
+      </c>
+      <c r="L104" t="s">
+        <v>24</v>
+      </c>
+      <c r="M104" t="s">
         <v>54</v>
       </c>
-      <c r="L104" t="s">
-        <v>24</v>
-      </c>
-      <c r="M104" t="s">
-        <v>55</v>
-      </c>
       <c r="P104" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
     </row>
     <row r="105" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B105" t="s">
-        <v>74</v>
+        <v>346</v>
       </c>
       <c r="D105" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E105" t="s">
         <v>20</v>
@@ -6259,24 +6259,24 @@
         <v>0.3301</v>
       </c>
       <c r="K105" t="s">
+        <v>53</v>
+      </c>
+      <c r="L105" t="s">
+        <v>24</v>
+      </c>
+      <c r="M105" t="s">
         <v>54</v>
       </c>
-      <c r="L105" t="s">
-        <v>24</v>
-      </c>
-      <c r="M105" t="s">
-        <v>55</v>
-      </c>
       <c r="P105" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
     </row>
     <row r="106" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B106" t="s">
-        <v>77</v>
+        <v>343</v>
       </c>
       <c r="D106" t="s">
         <v>19</v>
@@ -6303,21 +6303,21 @@
         <v>0.10741299999999999</v>
       </c>
       <c r="L106" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M106" t="s">
         <v>24</v>
       </c>
       <c r="P106" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
     <row r="107" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B107" t="s">
-        <v>77</v>
+        <v>343</v>
       </c>
       <c r="D107" t="s">
         <v>19</v>
@@ -6344,21 +6344,21 @@
         <v>0.10151300000000001</v>
       </c>
       <c r="L107" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M107" t="s">
         <v>24</v>
       </c>
       <c r="P107" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
     <row r="108" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B108" t="s">
-        <v>77</v>
+        <v>343</v>
       </c>
       <c r="D108" t="s">
         <v>19</v>
@@ -6385,21 +6385,21 @@
         <v>9.6590999999999996E-2</v>
       </c>
       <c r="L108" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M108" t="s">
         <v>24</v>
       </c>
       <c r="P108" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
     <row r="109" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B109" t="s">
-        <v>77</v>
+        <v>343</v>
       </c>
       <c r="D109" t="s">
         <v>19</v>
@@ -6426,21 +6426,21 @@
         <v>9.6365000000000006E-2</v>
       </c>
       <c r="L109" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M109" t="s">
         <v>24</v>
       </c>
       <c r="P109" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
     <row r="110" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B110" t="s">
-        <v>79</v>
+        <v>352</v>
       </c>
       <c r="D110" t="s">
         <v>19</v>
@@ -6467,21 +6467,21 @@
         <v>0.12497055999999999</v>
       </c>
       <c r="L110" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M110" t="s">
         <v>24</v>
       </c>
       <c r="P110" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
     <row r="111" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B111" t="s">
-        <v>79</v>
+        <v>352</v>
       </c>
       <c r="D111" t="s">
         <v>19</v>
@@ -6508,21 +6508,21 @@
         <v>0.11219999999999999</v>
       </c>
       <c r="L111" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M111" t="s">
         <v>24</v>
       </c>
       <c r="P111" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
     <row r="112" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B112" t="s">
-        <v>79</v>
+        <v>352</v>
       </c>
       <c r="D112" t="s">
         <v>19</v>
@@ -6549,21 +6549,21 @@
         <v>0.1097404</v>
       </c>
       <c r="L112" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M112" t="s">
         <v>24</v>
       </c>
       <c r="P112" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
     <row r="113" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B113" t="s">
-        <v>79</v>
+        <v>352</v>
       </c>
       <c r="D113" t="s">
         <v>19</v>
@@ -6590,21 +6590,21 @@
         <v>0.10254552</v>
       </c>
       <c r="L113" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M113" t="s">
         <v>24</v>
       </c>
       <c r="P113" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
     <row r="114" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B114" t="s">
-        <v>80</v>
+        <v>353</v>
       </c>
       <c r="D114" t="s">
         <v>19</v>
@@ -6631,21 +6631,21 @@
         <v>0.12989999999999999</v>
       </c>
       <c r="L114" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M114" t="s">
         <v>24</v>
       </c>
       <c r="P114" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
     <row r="115" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B115" t="s">
-        <v>80</v>
+        <v>353</v>
       </c>
       <c r="D115" t="s">
         <v>19</v>
@@ -6672,21 +6672,21 @@
         <v>0.1166625</v>
       </c>
       <c r="L115" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M115" t="s">
         <v>24</v>
       </c>
       <c r="P115" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
     <row r="116" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B116" t="s">
-        <v>80</v>
+        <v>353</v>
       </c>
       <c r="D116" t="s">
         <v>19</v>
@@ -6713,21 +6713,21 @@
         <v>0.114105075</v>
       </c>
       <c r="L116" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M116" t="s">
         <v>24</v>
       </c>
       <c r="P116" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
     <row r="117" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B117" t="s">
-        <v>80</v>
+        <v>353</v>
       </c>
       <c r="D117" t="s">
         <v>19</v>
@@ -6754,21 +6754,21 @@
         <v>0.10662403500000001</v>
       </c>
       <c r="L117" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M117" t="s">
         <v>24</v>
       </c>
       <c r="P117" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
     <row r="118" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B118" t="s">
-        <v>81</v>
+        <v>354</v>
       </c>
       <c r="D118" t="s">
         <v>19</v>
@@ -6795,21 +6795,21 @@
         <v>0.13491139999999999</v>
       </c>
       <c r="L118" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M118" t="s">
         <v>24</v>
       </c>
       <c r="P118" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
     <row r="119" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B119" t="s">
-        <v>81</v>
+        <v>354</v>
       </c>
       <c r="D119" t="s">
         <v>19</v>
@@ -6836,21 +6836,21 @@
         <v>0.121125</v>
       </c>
       <c r="L119" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M119" t="s">
         <v>24</v>
       </c>
       <c r="P119" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
     <row r="120" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B120" t="s">
-        <v>81</v>
+        <v>354</v>
       </c>
       <c r="D120" t="s">
         <v>19</v>
@@ -6877,21 +6877,21 @@
         <v>0.11846975</v>
       </c>
       <c r="L120" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M120" t="s">
         <v>24</v>
       </c>
       <c r="P120" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
     <row r="121" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B121" t="s">
-        <v>81</v>
+        <v>354</v>
       </c>
       <c r="D121" t="s">
         <v>19</v>
@@ -6918,21 +6918,21 @@
         <v>0.11070255</v>
       </c>
       <c r="L121" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M121" t="s">
         <v>24</v>
       </c>
       <c r="P121" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
     <row r="122" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B122" t="s">
-        <v>82</v>
+        <v>355</v>
       </c>
       <c r="D122" t="s">
         <v>19</v>
@@ -6959,21 +6959,21 @@
         <v>0.127</v>
       </c>
       <c r="L122" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M122" t="s">
         <v>24</v>
       </c>
       <c r="P122" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
     <row r="123" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B123" t="s">
-        <v>82</v>
+        <v>355</v>
       </c>
       <c r="D123" t="s">
         <v>19</v>
@@ -7000,21 +7000,21 @@
         <v>0.11459999999999999</v>
       </c>
       <c r="L123" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M123" t="s">
         <v>24</v>
       </c>
       <c r="P123" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
     <row r="124" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B124" t="s">
-        <v>82</v>
+        <v>355</v>
       </c>
       <c r="D124" t="s">
         <v>19</v>
@@ -7041,21 +7041,21 @@
         <v>0.1116</v>
       </c>
       <c r="L124" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M124" t="s">
         <v>24</v>
       </c>
       <c r="P124" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
     <row r="125" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B125" t="s">
-        <v>82</v>
+        <v>355</v>
       </c>
       <c r="D125" t="s">
         <v>19</v>
@@ -7082,21 +7082,21 @@
         <v>0.10539999999999999</v>
       </c>
       <c r="L125" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M125" t="s">
         <v>24</v>
       </c>
       <c r="P125" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
     <row r="126" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B126" t="s">
-        <v>83</v>
+        <v>356</v>
       </c>
       <c r="D126" t="s">
         <v>19</v>
@@ -7123,21 +7123,21 @@
         <v>9.7289600000000004E-2</v>
       </c>
       <c r="L126" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M126" t="s">
         <v>24</v>
       </c>
       <c r="P126" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
     <row r="127" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B127" t="s">
-        <v>83</v>
+        <v>356</v>
       </c>
       <c r="D127" t="s">
         <v>19</v>
@@ -7164,21 +7164,21 @@
         <v>9.5616000000000007E-2</v>
       </c>
       <c r="L127" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M127" t="s">
         <v>24</v>
       </c>
       <c r="P127" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
     <row r="128" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B128" t="s">
-        <v>83</v>
+        <v>356</v>
       </c>
       <c r="D128" t="s">
         <v>19</v>
@@ -7205,21 +7205,21 @@
         <v>9.4696799999999998E-2</v>
       </c>
       <c r="L128" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M128" t="s">
         <v>24</v>
       </c>
       <c r="P128" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
     <row r="129" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B129" t="s">
-        <v>83</v>
+        <v>356</v>
       </c>
       <c r="D129" t="s">
         <v>19</v>
@@ -7246,24 +7246,24 @@
         <v>9.3031199999999994E-2</v>
       </c>
       <c r="L129" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M129" t="s">
         <v>24</v>
       </c>
       <c r="P129" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
     <row r="130" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B130" t="s">
-        <v>84</v>
+        <v>344</v>
       </c>
       <c r="D130" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E130" t="s">
         <v>20</v>
@@ -7284,27 +7284,27 @@
         <v>0.11559999999999999</v>
       </c>
       <c r="K130" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="L130" t="s">
+        <v>24</v>
+      </c>
+      <c r="M130" t="s">
         <v>54</v>
       </c>
-      <c r="L130" t="s">
-        <v>24</v>
-      </c>
-      <c r="M130" t="s">
-        <v>55</v>
-      </c>
       <c r="P130" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
     <row r="131" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B131" t="s">
-        <v>84</v>
+        <v>344</v>
       </c>
       <c r="D131" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E131" t="s">
         <v>20</v>
@@ -7325,27 +7325,27 @@
         <v>0.1497</v>
       </c>
       <c r="K131" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="L131" t="s">
+        <v>24</v>
+      </c>
+      <c r="M131" t="s">
         <v>54</v>
       </c>
-      <c r="L131" t="s">
-        <v>24</v>
-      </c>
-      <c r="M131" t="s">
-        <v>55</v>
-      </c>
       <c r="P131" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
     <row r="132" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B132" t="s">
-        <v>84</v>
+        <v>344</v>
       </c>
       <c r="D132" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E132" t="s">
         <v>20</v>
@@ -7366,27 +7366,27 @@
         <v>0.1827</v>
       </c>
       <c r="K132" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="L132" t="s">
+        <v>24</v>
+      </c>
+      <c r="M132" t="s">
         <v>54</v>
       </c>
-      <c r="L132" t="s">
-        <v>24</v>
-      </c>
-      <c r="M132" t="s">
-        <v>55</v>
-      </c>
       <c r="P132" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
     <row r="133" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B133" t="s">
-        <v>84</v>
+        <v>344</v>
       </c>
       <c r="D133" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E133" t="s">
         <v>20</v>
@@ -7407,24 +7407,24 @@
         <v>0.2364</v>
       </c>
       <c r="K133" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="L133" t="s">
+        <v>24</v>
+      </c>
+      <c r="M133" t="s">
         <v>54</v>
       </c>
-      <c r="L133" t="s">
-        <v>24</v>
-      </c>
-      <c r="M133" t="s">
-        <v>55</v>
-      </c>
       <c r="P133" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
     <row r="134" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="B134" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="D134" t="s">
         <v>19</v>
@@ -7457,15 +7457,15 @@
         <v>24</v>
       </c>
       <c r="P134" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
     </row>
     <row r="135" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="B135" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="D135" t="s">
         <v>19</v>
@@ -7498,15 +7498,15 @@
         <v>24</v>
       </c>
       <c r="P135" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
     </row>
     <row r="136" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="B136" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="D136" t="s">
         <v>19</v>
@@ -7539,15 +7539,15 @@
         <v>24</v>
       </c>
       <c r="P136" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
     </row>
     <row r="137" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="B137" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="D137" t="s">
         <v>19</v>
@@ -7580,15 +7580,15 @@
         <v>24</v>
       </c>
       <c r="P137" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
     </row>
     <row r="138" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="B138" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="D138" t="s">
         <v>19</v>
@@ -7621,15 +7621,15 @@
         <v>24</v>
       </c>
       <c r="P138" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
     </row>
     <row r="139" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="B139" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="D139" t="s">
         <v>19</v>
@@ -7662,15 +7662,15 @@
         <v>24</v>
       </c>
       <c r="P139" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
     </row>
     <row r="140" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="B140" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="D140" t="s">
         <v>19</v>
@@ -7703,15 +7703,15 @@
         <v>24</v>
       </c>
       <c r="P140" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
     </row>
     <row r="141" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="B141" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="D141" t="s">
         <v>19</v>
@@ -7744,15 +7744,15 @@
         <v>24</v>
       </c>
       <c r="P141" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
     </row>
     <row r="142" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="B142" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="D142" t="s">
         <v>19</v>
@@ -7785,15 +7785,15 @@
         <v>24</v>
       </c>
       <c r="P142" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
     </row>
     <row r="143" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="B143" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="D143" t="s">
         <v>19</v>
@@ -7826,15 +7826,15 @@
         <v>24</v>
       </c>
       <c r="P143" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
     </row>
     <row r="144" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="B144" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="D144" t="s">
         <v>19</v>
@@ -7867,15 +7867,15 @@
         <v>24</v>
       </c>
       <c r="P144" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
     </row>
     <row r="145" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="B145" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="D145" t="s">
         <v>19</v>
@@ -7908,15 +7908,15 @@
         <v>24</v>
       </c>
       <c r="P145" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
     </row>
     <row r="146" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="B146" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="D146" t="s">
         <v>19</v>
@@ -7949,15 +7949,15 @@
         <v>24</v>
       </c>
       <c r="P146" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
     </row>
     <row r="147" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="B147" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="D147" t="s">
         <v>19</v>
@@ -7990,15 +7990,15 @@
         <v>24</v>
       </c>
       <c r="P147" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
     </row>
     <row r="148" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="B148" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="D148" t="s">
         <v>19</v>
@@ -8031,15 +8031,15 @@
         <v>24</v>
       </c>
       <c r="P148" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
     </row>
     <row r="149" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="B149" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="D149" t="s">
         <v>19</v>
@@ -8072,18 +8072,18 @@
         <v>24</v>
       </c>
       <c r="P149" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
     </row>
     <row r="150" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="B150" t="s">
-        <v>94</v>
+        <v>342</v>
       </c>
       <c r="D150" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E150" t="s">
         <v>20</v>
@@ -8104,27 +8104,27 @@
         <v>7.0839240506329101E-2</v>
       </c>
       <c r="K150" t="s">
+        <v>53</v>
+      </c>
+      <c r="L150" t="s">
+        <v>24</v>
+      </c>
+      <c r="M150" t="s">
         <v>54</v>
       </c>
-      <c r="L150" t="s">
-        <v>24</v>
-      </c>
-      <c r="M150" t="s">
-        <v>55</v>
-      </c>
       <c r="P150" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
     </row>
     <row r="151" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="B151" t="s">
-        <v>94</v>
+        <v>342</v>
       </c>
       <c r="D151" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E151" t="s">
         <v>20</v>
@@ -8145,27 +8145,27 @@
         <v>0.102263461538462</v>
       </c>
       <c r="K151" t="s">
+        <v>53</v>
+      </c>
+      <c r="L151" t="s">
+        <v>24</v>
+      </c>
+      <c r="M151" t="s">
         <v>54</v>
       </c>
-      <c r="L151" t="s">
-        <v>24</v>
-      </c>
-      <c r="M151" t="s">
-        <v>55</v>
-      </c>
       <c r="P151" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
     </row>
     <row r="152" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="B152" t="s">
-        <v>94</v>
+        <v>342</v>
       </c>
       <c r="D152" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E152" t="s">
         <v>20</v>
@@ -8186,27 +8186,27 @@
         <v>0.13722317073170701</v>
       </c>
       <c r="K152" t="s">
+        <v>53</v>
+      </c>
+      <c r="L152" t="s">
+        <v>24</v>
+      </c>
+      <c r="M152" t="s">
         <v>54</v>
       </c>
-      <c r="L152" t="s">
-        <v>24</v>
-      </c>
-      <c r="M152" t="s">
-        <v>55</v>
-      </c>
       <c r="P152" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
     </row>
     <row r="153" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="B153" t="s">
-        <v>94</v>
+        <v>342</v>
       </c>
       <c r="D153" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E153" t="s">
         <v>20</v>
@@ -8227,24 +8227,24 @@
         <v>0.1827</v>
       </c>
       <c r="K153" t="s">
+        <v>53</v>
+      </c>
+      <c r="L153" t="s">
+        <v>24</v>
+      </c>
+      <c r="M153" t="s">
         <v>54</v>
       </c>
-      <c r="L153" t="s">
-        <v>24</v>
-      </c>
-      <c r="M153" t="s">
-        <v>55</v>
-      </c>
       <c r="P153" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
     </row>
     <row r="154" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="B154" t="s">
-        <v>355</v>
+        <v>340</v>
       </c>
       <c r="D154" t="s">
         <v>19</v>
@@ -8277,18 +8277,18 @@
         <v>24</v>
       </c>
       <c r="P154" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="S154" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
     </row>
     <row r="155" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="B155" t="s">
-        <v>355</v>
+        <v>340</v>
       </c>
       <c r="D155" t="s">
         <v>19</v>
@@ -8321,15 +8321,15 @@
         <v>24</v>
       </c>
       <c r="P155" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
     </row>
     <row r="156" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="B156" t="s">
-        <v>355</v>
+        <v>340</v>
       </c>
       <c r="D156" t="s">
         <v>19</v>
@@ -8362,15 +8362,15 @@
         <v>24</v>
       </c>
       <c r="P156" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
     </row>
     <row r="157" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="B157" t="s">
-        <v>356</v>
+        <v>341</v>
       </c>
       <c r="D157" t="s">
         <v>19</v>
@@ -8403,7 +8403,7 @@
         <v>24</v>
       </c>
       <c r="P157" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -8416,13 +8416,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B1462"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -20128,15 +20131,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="B2" s="1">
         <v>46184</v>
@@ -20162,19 +20165,19 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="B1" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="C1" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="D1" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="E1" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="F1" t="s">
         <v>15</v>
@@ -20182,7 +20185,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -20191,18 +20194,18 @@
         <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="E2" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="F2" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -20211,18 +20214,18 @@
         <v>0</v>
       </c>
       <c r="D3" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="E3" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="F3" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -20231,18 +20234,18 @@
         <v>0</v>
       </c>
       <c r="D4" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="E4" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="F4" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -20251,18 +20254,18 @@
         <v>0</v>
       </c>
       <c r="D5" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="E5" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="F5" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -20271,18 +20274,18 @@
         <v>0</v>
       </c>
       <c r="D6" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="E6" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="F6" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -20291,18 +20294,18 @@
         <v>0</v>
       </c>
       <c r="D7" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="E7" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="F7" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B8">
         <v>3.4684899999999999E-3</v>
@@ -20311,18 +20314,18 @@
         <v>2.9795799999999999E-3</v>
       </c>
       <c r="D8" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="E8" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="F8" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="B9">
         <v>1.1611679999999999E-2</v>
@@ -20331,18 +20334,18 @@
         <v>9.9749399999999998E-3</v>
       </c>
       <c r="D9" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="E9" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="F9" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -20351,18 +20354,18 @@
         <v>0</v>
       </c>
       <c r="D10" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="E10" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="F10" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="B11">
         <v>4.2528599999999998E-3</v>
@@ -20371,18 +20374,18 @@
         <v>3.6533899999999998E-3</v>
       </c>
       <c r="D11" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="E11" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="F11" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -20391,18 +20394,18 @@
         <v>0</v>
       </c>
       <c r="D12" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="E12" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="F12" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -20411,18 +20414,18 @@
         <v>0</v>
       </c>
       <c r="D13" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="E13" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="F13" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="B14">
         <v>2.4159300000000002E-3</v>
@@ -20431,18 +20434,18 @@
         <v>2.0753899999999999E-3</v>
       </c>
       <c r="D14" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="E14" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="F14" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="B15">
         <v>8.6965299999999992E-3</v>
@@ -20451,18 +20454,18 @@
         <v>7.4707000000000003E-3</v>
       </c>
       <c r="D15" t="s">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c r="E15" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="F15" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -20471,18 +20474,18 @@
         <v>0</v>
       </c>
       <c r="D16" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="E16" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="F16" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -20491,18 +20494,18 @@
         <v>0</v>
       </c>
       <c r="D17" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="E17" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="F17" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -20511,18 +20514,18 @@
         <v>0</v>
       </c>
       <c r="D18" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="E18" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="F18" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="B19">
         <v>1.28383E-2</v>
@@ -20531,18 +20534,18 @@
         <v>1.1028659999999999E-2</v>
       </c>
       <c r="D19" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="E19" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="F19" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="B20">
         <v>4.3978699999999999E-3</v>
@@ -20551,18 +20554,18 @@
         <v>3.7779699999999999E-3</v>
       </c>
       <c r="D20" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="E20" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="F20" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="B21">
         <v>7.07524E-3</v>
@@ -20571,18 +20574,18 @@
         <v>6.0779400000000004E-3</v>
       </c>
       <c r="D21" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="E21" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="F21" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -20591,18 +20594,18 @@
         <v>0</v>
       </c>
       <c r="D22" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="E22" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="F22" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="B23">
         <v>4.7299999999999996E-6</v>
@@ -20611,18 +20614,18 @@
         <v>4.0600000000000001E-6</v>
       </c>
       <c r="D23" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="E23" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="F23" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="B24">
         <v>3.0895679999999998E-2</v>
@@ -20631,18 +20634,18 @@
         <v>2.6540749999999998E-2</v>
       </c>
       <c r="D24" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="E24" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="F24" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -20651,18 +20654,18 @@
         <v>0</v>
       </c>
       <c r="D25" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="E25" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="F25" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -20671,18 +20674,18 @@
         <v>0</v>
       </c>
       <c r="D26" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="E26" t="s">
-        <v>152</v>
+        <v>138</v>
       </c>
       <c r="F26" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -20691,18 +20694,18 @@
         <v>0</v>
       </c>
       <c r="D27" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="E27" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="F27" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>154</v>
+        <v>140</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -20711,18 +20714,18 @@
         <v>0</v>
       </c>
       <c r="D28" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="E28" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="F28" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>155</v>
+        <v>141</v>
       </c>
       <c r="B29">
         <v>1.3180900000000001E-3</v>
@@ -20731,18 +20734,18 @@
         <v>1.13229E-3</v>
       </c>
       <c r="D29" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="E29" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="F29" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -20751,18 +20754,18 @@
         <v>0</v>
       </c>
       <c r="D30" t="s">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c r="E30" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="F30" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -20771,18 +20774,18 @@
         <v>0</v>
       </c>
       <c r="D31" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="E31" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="F31" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -20791,18 +20794,18 @@
         <v>0</v>
       </c>
       <c r="D32" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="E32" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="F32" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -20811,18 +20814,18 @@
         <v>0</v>
       </c>
       <c r="D33" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="E33" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="F33" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -20831,18 +20834,18 @@
         <v>0</v>
       </c>
       <c r="D34" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="E34" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="F34" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -20851,18 +20854,18 @@
         <v>0</v>
       </c>
       <c r="D35" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="E35" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="F35" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -20871,18 +20874,18 @@
         <v>0</v>
       </c>
       <c r="D36" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="E36" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="F36" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -20891,18 +20894,18 @@
         <v>0</v>
       </c>
       <c r="D37" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="E37" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="F37" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>164</v>
+        <v>150</v>
       </c>
       <c r="B38">
         <v>1.6042899999999999E-2</v>
@@ -20911,18 +20914,18 @@
         <v>1.378155E-2</v>
       </c>
       <c r="D38" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="E38" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="F38" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="B39">
         <v>1.6049600000000001E-2</v>
@@ -20931,18 +20934,18 @@
         <v>1.3787310000000001E-2</v>
       </c>
       <c r="D39" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="E39" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="F39" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -20951,18 +20954,18 @@
         <v>0</v>
       </c>
       <c r="D40" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="E40" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="F40" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>169</v>
+        <v>155</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -20971,18 +20974,18 @@
         <v>0</v>
       </c>
       <c r="D41" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="E41" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="F41" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>170</v>
+        <v>156</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -20991,18 +20994,18 @@
         <v>0</v>
       </c>
       <c r="D42" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="E42" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="F42" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>171</v>
+        <v>157</v>
       </c>
       <c r="B43">
         <v>4.38719E-3</v>
@@ -21011,18 +21014,18 @@
         <v>3.7687900000000002E-3</v>
       </c>
       <c r="D43" t="s">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c r="E43" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="F43" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
       <c r="B44">
         <v>5.8240699999999998E-3</v>
@@ -21031,18 +21034,18 @@
         <v>5.0031299999999997E-3</v>
       </c>
       <c r="D44" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="E44" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="F44" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="B45">
         <v>5.0403100000000001E-3</v>
@@ -21051,18 +21054,18 @@
         <v>4.3298499999999997E-3</v>
       </c>
       <c r="D45" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="E45" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="F45" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -21071,18 +21074,18 @@
         <v>0</v>
       </c>
       <c r="D46" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="E46" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="F46" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>175</v>
+        <v>161</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -21091,18 +21094,18 @@
         <v>0</v>
       </c>
       <c r="D47" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="E47" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="F47" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>176</v>
+        <v>162</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -21111,18 +21114,18 @@
         <v>0</v>
       </c>
       <c r="D48" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="E48" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="F48" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -21131,18 +21134,18 @@
         <v>0</v>
       </c>
       <c r="D49" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="E49" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="F49" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -21151,18 +21154,18 @@
         <v>0</v>
       </c>
       <c r="D50" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="E50" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="F50" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>179</v>
+        <v>165</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -21171,18 +21174,18 @@
         <v>0</v>
       </c>
       <c r="D51" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="E51" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="F51" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>180</v>
+        <v>166</v>
       </c>
       <c r="B52">
         <v>1.609E-5</v>
@@ -21191,18 +21194,18 @@
         <v>1.382E-5</v>
       </c>
       <c r="D52" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="E52" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="F52" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B53">
         <v>6.5729200000000003E-3</v>
@@ -21211,18 +21214,18 @@
         <v>5.64643E-3</v>
       </c>
       <c r="D53" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="E53" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="F53" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="B54">
         <v>1.8657730000000001E-2</v>
@@ -21231,18 +21234,18 @@
         <v>1.602781E-2</v>
       </c>
       <c r="D54" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="E54" t="s">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="F54" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="B55">
         <v>1.6368299999999999E-3</v>
@@ -21251,18 +21254,18 @@
         <v>1.4061099999999999E-3</v>
       </c>
       <c r="D55" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="E55" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="F55" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -21271,18 +21274,18 @@
         <v>0</v>
       </c>
       <c r="D56" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="E56" t="s">
-        <v>188</v>
+        <v>174</v>
       </c>
       <c r="F56" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -21291,18 +21294,18 @@
         <v>0</v>
       </c>
       <c r="D57" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="E57" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="F57" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="B58">
         <v>1.541E-5</v>
@@ -21311,18 +21314,18 @@
         <v>1.324E-5</v>
       </c>
       <c r="D58" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="E58" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="F58" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>191</v>
+        <v>177</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -21331,18 +21334,18 @@
         <v>0</v>
       </c>
       <c r="D59" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="E59" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="F59" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="B60">
         <v>2.8363300000000002E-3</v>
@@ -21351,18 +21354,18 @@
         <v>2.4365300000000001E-3</v>
       </c>
       <c r="D60" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="E60" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="F60" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -21371,18 +21374,18 @@
         <v>0</v>
       </c>
       <c r="D61" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="E61" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="F61" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>194</v>
+        <v>180</v>
       </c>
       <c r="B62">
         <v>9.9309000000000008E-4</v>
@@ -21391,18 +21394,18 @@
         <v>8.5309999999999997E-4</v>
       </c>
       <c r="D62" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="E62" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="F62" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -21411,18 +21414,18 @@
         <v>0</v>
       </c>
       <c r="D63" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="E63" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="F63" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="B64">
         <v>3.8569099999999999E-3</v>
@@ -21431,18 +21434,18 @@
         <v>3.3132600000000002E-3</v>
       </c>
       <c r="D64" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="E64" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="F64" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>197</v>
+        <v>183</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -21451,18 +21454,18 @@
         <v>0</v>
       </c>
       <c r="D65" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="E65" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="F65" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="B66">
         <v>5.8233699999999996E-3</v>
@@ -21471,18 +21474,18 @@
         <v>5.0025299999999998E-3</v>
       </c>
       <c r="D66" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="E66" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="F66" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -21491,18 +21494,18 @@
         <v>0</v>
       </c>
       <c r="D67" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="E67" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="F67" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>200</v>
+        <v>186</v>
       </c>
       <c r="B68">
         <v>4.4916699999999997E-3</v>
@@ -21511,18 +21514,18 @@
         <v>3.8585500000000001E-3</v>
       </c>
       <c r="D68" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="E68" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="F68" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>201</v>
+        <v>187</v>
       </c>
       <c r="B69">
         <v>7.0537899999999999E-3</v>
@@ -21531,18 +21534,18 @@
         <v>6.0595099999999997E-3</v>
       </c>
       <c r="D69" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="E69" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="F69" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>202</v>
+        <v>188</v>
       </c>
       <c r="B70">
         <v>1.0788590000000001E-2</v>
@@ -21551,18 +21554,18 @@
         <v>9.2678799999999992E-3</v>
       </c>
       <c r="D70" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="E70" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="F70" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>203</v>
+        <v>189</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -21571,18 +21574,18 @@
         <v>0</v>
       </c>
       <c r="D71" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="E71" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="F71" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -21591,18 +21594,18 @@
         <v>0</v>
       </c>
       <c r="D72" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="E72" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="F72" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>205</v>
+        <v>191</v>
       </c>
       <c r="B73">
         <v>4.2203800000000001E-3</v>
@@ -21611,18 +21614,18 @@
         <v>3.6254899999999999E-3</v>
       </c>
       <c r="D73" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="E73" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="F73" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="B74">
         <v>6.9173799999999999E-3</v>
@@ -21631,18 +21634,18 @@
         <v>5.94233E-3</v>
       </c>
       <c r="D74" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="E74" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="F74" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>207</v>
+        <v>193</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -21651,18 +21654,18 @@
         <v>0</v>
       </c>
       <c r="D75" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="E75" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="F75" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>208</v>
+        <v>194</v>
       </c>
       <c r="B76">
         <v>0</v>
@@ -21671,18 +21674,18 @@
         <v>0</v>
       </c>
       <c r="D76" t="s">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c r="E76" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="F76" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>209</v>
+        <v>195</v>
       </c>
       <c r="B77">
         <v>0</v>
@@ -21691,18 +21694,18 @@
         <v>0</v>
       </c>
       <c r="D77" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="E77" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="F77" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>210</v>
+        <v>196</v>
       </c>
       <c r="B78">
         <v>5.3032499999999998E-3</v>
@@ -21711,18 +21714,18 @@
         <v>4.5557200000000001E-3</v>
       </c>
       <c r="D78" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="E78" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="F78" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -21731,18 +21734,18 @@
         <v>0</v>
       </c>
       <c r="D79" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="E79" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="F79" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -21751,18 +21754,18 @@
         <v>0</v>
       </c>
       <c r="D80" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="E80" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="F80" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -21771,18 +21774,18 @@
         <v>0</v>
       </c>
       <c r="D81" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="E81" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="F81" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -21791,18 +21794,18 @@
         <v>0</v>
       </c>
       <c r="D82" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="E82" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="F82" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -21811,18 +21814,18 @@
         <v>0</v>
       </c>
       <c r="D83" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="E83" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="F83" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
       <c r="B84">
         <v>3.19002E-3</v>
@@ -21831,18 +21834,18 @@
         <v>2.7403699999999998E-3</v>
       </c>
       <c r="D84" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="E84" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="F84" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>217</v>
+        <v>203</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -21851,18 +21854,18 @@
         <v>0</v>
       </c>
       <c r="D85" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="E85" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="F85" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="B86">
         <v>1.4809839999999999E-2</v>
@@ -21871,18 +21874,18 @@
         <v>1.2722300000000001E-2</v>
       </c>
       <c r="D86" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="E86" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="F86" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -21891,18 +21894,18 @@
         <v>0</v>
       </c>
       <c r="D87" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="E87" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="F87" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -21911,18 +21914,18 @@
         <v>0</v>
       </c>
       <c r="D88" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="E88" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="F88" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -21931,18 +21934,18 @@
         <v>0</v>
       </c>
       <c r="D89" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="E89" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="F89" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -21951,18 +21954,18 @@
         <v>0</v>
       </c>
       <c r="D90" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="E90" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="F90" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>223</v>
+        <v>209</v>
       </c>
       <c r="B91">
         <v>1.6499100000000001E-3</v>
@@ -21971,18 +21974,18 @@
         <v>1.4173499999999999E-3</v>
       </c>
       <c r="D91" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="E91" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="F91" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -21991,18 +21994,18 @@
         <v>0</v>
       </c>
       <c r="D92" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="E92" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="F92" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -22011,18 +22014,18 @@
         <v>0</v>
       </c>
       <c r="D93" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="E93" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="F93" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>226</v>
+        <v>212</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -22031,18 +22034,18 @@
         <v>0</v>
       </c>
       <c r="D94" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="E94" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="F94" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>227</v>
+        <v>213</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -22051,18 +22054,18 @@
         <v>0</v>
       </c>
       <c r="D95" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="E95" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="F95" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -22071,18 +22074,18 @@
         <v>0</v>
       </c>
       <c r="D96" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="E96" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="F96" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>229</v>
+        <v>215</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -22091,18 +22094,18 @@
         <v>0</v>
       </c>
       <c r="D97" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="E97" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="F97" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="B98">
         <v>9.1582199999999999E-3</v>
@@ -22111,18 +22114,18 @@
         <v>7.8673100000000006E-3</v>
       </c>
       <c r="D98" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="E98" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="F98" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>231</v>
+        <v>217</v>
       </c>
       <c r="B99">
         <v>6.67637E-3</v>
@@ -22131,18 +22134,18 @@
         <v>5.7352999999999996E-3</v>
       </c>
       <c r="D99" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="E99" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="F99" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>232</v>
+        <v>218</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -22151,18 +22154,18 @@
         <v>0</v>
       </c>
       <c r="D100" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="E100" t="s">
-        <v>188</v>
+        <v>174</v>
       </c>
       <c r="F100" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>233</v>
+        <v>219</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -22171,18 +22174,18 @@
         <v>0</v>
       </c>
       <c r="D101" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="E101" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="F101" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>234</v>
+        <v>220</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -22191,18 +22194,18 @@
         <v>0</v>
       </c>
       <c r="D102" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="E102" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="F102" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>235</v>
+        <v>221</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -22211,18 +22214,18 @@
         <v>0</v>
       </c>
       <c r="D103" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="E103" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="F103" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>236</v>
+        <v>222</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -22231,18 +22234,18 @@
         <v>0</v>
       </c>
       <c r="D104" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="E104" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="F104" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>237</v>
+        <v>223</v>
       </c>
       <c r="B105">
         <v>5.6688900000000002E-3</v>
@@ -22251,18 +22254,18 @@
         <v>4.8698300000000003E-3</v>
       </c>
       <c r="D105" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="E105" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="F105" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>238</v>
+        <v>224</v>
       </c>
       <c r="B106">
         <v>3.3768100000000001E-3</v>
@@ -22271,18 +22274,18 @@
         <v>2.9008300000000001E-3</v>
       </c>
       <c r="D106" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="E106" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="F106" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>239</v>
+        <v>225</v>
       </c>
       <c r="B107">
         <v>4.6591799999999997E-3</v>
@@ -22291,18 +22294,18 @@
         <v>4.0024400000000003E-3</v>
       </c>
       <c r="D107" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="E107" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="F107" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>240</v>
+        <v>226</v>
       </c>
       <c r="B108">
         <v>1.9069499999999999E-3</v>
@@ -22311,18 +22314,18 @@
         <v>1.6381600000000001E-3</v>
       </c>
       <c r="D108" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="E108" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="F108" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -22331,18 +22334,18 @@
         <v>0</v>
       </c>
       <c r="D109" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="E109" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="F109" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>242</v>
+        <v>228</v>
       </c>
       <c r="B110">
         <v>5.3588300000000002E-3</v>
@@ -22351,18 +22354,18 @@
         <v>4.6034700000000001E-3</v>
       </c>
       <c r="D110" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="E110" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="F110" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -22371,18 +22374,18 @@
         <v>0</v>
       </c>
       <c r="D111" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="E111" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="F111" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>244</v>
+        <v>230</v>
       </c>
       <c r="B112">
         <v>3.2703900000000002E-3</v>
@@ -22391,18 +22394,18 @@
         <v>2.80941E-3</v>
       </c>
       <c r="D112" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="E112" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="F112" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -22411,18 +22414,18 @@
         <v>0</v>
       </c>
       <c r="D113" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="E113" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="F113" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>246</v>
+        <v>232</v>
       </c>
       <c r="B114">
         <v>0</v>
@@ -22431,18 +22434,18 @@
         <v>0</v>
       </c>
       <c r="D114" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="E114" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="F114" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="B115">
         <v>0</v>
@@ -22451,18 +22454,18 @@
         <v>0</v>
       </c>
       <c r="D115" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="E115" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="F115" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="B116">
         <v>0</v>
@@ -22471,18 +22474,18 @@
         <v>0</v>
       </c>
       <c r="D116" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="E116" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="F116" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
       <c r="B117">
         <v>0</v>
@@ -22491,18 +22494,18 @@
         <v>0</v>
       </c>
       <c r="D117" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="E117" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="F117" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>250</v>
+        <v>236</v>
       </c>
       <c r="B118">
         <v>4.0392600000000002E-3</v>
@@ -22511,18 +22514,18 @@
         <v>3.4699000000000002E-3</v>
       </c>
       <c r="D118" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="E118" t="s">
-        <v>188</v>
+        <v>174</v>
       </c>
       <c r="F118" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="B119">
         <v>2.1069499999999998E-3</v>
@@ -22531,18 +22534,18 @@
         <v>1.80996E-3</v>
       </c>
       <c r="D119" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="E119" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="F119" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="B120">
         <v>0</v>
@@ -22551,18 +22554,18 @@
         <v>0</v>
       </c>
       <c r="D120" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="E120" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="F120" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B121">
         <v>0</v>
@@ -22571,18 +22574,18 @@
         <v>0</v>
       </c>
       <c r="D121" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="E121" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="F121" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>254</v>
+        <v>240</v>
       </c>
       <c r="B122">
         <v>8.9892199999999992E-3</v>
@@ -22591,18 +22594,18 @@
         <v>7.7221399999999997E-3</v>
       </c>
       <c r="D122" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="E122" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="F122" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="B123">
         <v>0</v>
@@ -22611,18 +22614,18 @@
         <v>0</v>
       </c>
       <c r="D123" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="E123" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="F123" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>256</v>
+        <v>242</v>
       </c>
       <c r="B124">
         <v>0</v>
@@ -22631,18 +22634,18 @@
         <v>0</v>
       </c>
       <c r="D124" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="E124" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="F124" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>257</v>
+        <v>243</v>
       </c>
       <c r="B125">
         <v>0</v>
@@ -22651,18 +22654,18 @@
         <v>0</v>
       </c>
       <c r="D125" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="E125" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="F125" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>258</v>
+        <v>244</v>
       </c>
       <c r="B126">
         <v>0</v>
@@ -22671,18 +22674,18 @@
         <v>0</v>
       </c>
       <c r="D126" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="E126" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="F126" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>259</v>
+        <v>245</v>
       </c>
       <c r="B127">
         <v>0</v>
@@ -22691,18 +22694,18 @@
         <v>0</v>
       </c>
       <c r="D127" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="E127" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="F127" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>260</v>
+        <v>246</v>
       </c>
       <c r="B128">
         <v>2.1070799999999999E-3</v>
@@ -22711,18 +22714,18 @@
         <v>1.81007E-3</v>
       </c>
       <c r="D128" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="E128" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="F128" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>261</v>
+        <v>247</v>
       </c>
       <c r="B129">
         <v>0</v>
@@ -22731,18 +22734,18 @@
         <v>0</v>
       </c>
       <c r="D129" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="E129" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="F129" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>262</v>
+        <v>248</v>
       </c>
       <c r="B130">
         <v>6.0648300000000002E-3</v>
@@ -22751,18 +22754,18 @@
         <v>5.2099599999999996E-3</v>
       </c>
       <c r="D130" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="E130" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="F130" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>263</v>
+        <v>249</v>
       </c>
       <c r="B131">
         <v>6.4330799999999999E-3</v>
@@ -22771,18 +22774,18 @@
         <v>5.5262999999999996E-3</v>
       </c>
       <c r="D131" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="E131" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="F131" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>264</v>
+        <v>250</v>
       </c>
       <c r="B132">
         <v>0</v>
@@ -22791,18 +22794,18 @@
         <v>0</v>
       </c>
       <c r="D132" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="E132" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="F132" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="B133">
         <v>0</v>
@@ -22811,18 +22814,18 @@
         <v>0</v>
       </c>
       <c r="D133" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="E133" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="F133" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>266</v>
+        <v>252</v>
       </c>
       <c r="B134">
         <v>1.27568E-2</v>
@@ -22831,18 +22834,18 @@
         <v>1.095865E-2</v>
       </c>
       <c r="D134" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="E134" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="F134" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>267</v>
+        <v>253</v>
       </c>
       <c r="B135">
         <v>0</v>
@@ -22851,18 +22854,18 @@
         <v>0</v>
       </c>
       <c r="D135" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="E135" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="F135" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>268</v>
+        <v>254</v>
       </c>
       <c r="B136">
         <v>0</v>
@@ -22871,18 +22874,18 @@
         <v>0</v>
       </c>
       <c r="D136" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="E136" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="F136" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>269</v>
+        <v>255</v>
       </c>
       <c r="B137">
         <v>1.0773E-2</v>
@@ -22891,18 +22894,18 @@
         <v>9.2544800000000007E-3</v>
       </c>
       <c r="D137" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="E137" t="s">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="F137" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>270</v>
+        <v>256</v>
       </c>
       <c r="B138">
         <v>1.21697E-2</v>
@@ -22911,18 +22914,18 @@
         <v>1.04543E-2</v>
       </c>
       <c r="D138" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="E138" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="F138" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>271</v>
+        <v>257</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -22931,18 +22934,18 @@
         <v>0</v>
       </c>
       <c r="D139" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="E139" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="F139" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>272</v>
+        <v>258</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -22951,18 +22954,18 @@
         <v>0</v>
       </c>
       <c r="D140" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="E140" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="F140" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>273</v>
+        <v>259</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -22971,18 +22974,18 @@
         <v>0</v>
       </c>
       <c r="D141" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="E141" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="F141" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>274</v>
+        <v>260</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -22991,18 +22994,18 @@
         <v>0</v>
       </c>
       <c r="D142" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="E142" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="F142" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>275</v>
+        <v>261</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -23011,18 +23014,18 @@
         <v>0</v>
       </c>
       <c r="D143" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="E143" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="F143" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>276</v>
+        <v>262</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -23031,18 +23034,18 @@
         <v>0</v>
       </c>
       <c r="D144" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="E144" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="F144" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>277</v>
+        <v>263</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -23051,18 +23054,18 @@
         <v>0</v>
       </c>
       <c r="D145" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="E145" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="F145" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>278</v>
+        <v>264</v>
       </c>
       <c r="B146">
         <v>6.8610999999999998E-4</v>
@@ -23071,18 +23074,18 @@
         <v>5.8940000000000002E-4</v>
       </c>
       <c r="D146" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="E146" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="F146" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>279</v>
+        <v>265</v>
       </c>
       <c r="B147">
         <v>1.174541E-2</v>
@@ -23091,18 +23094,18 @@
         <v>1.0089829999999999E-2</v>
       </c>
       <c r="D147" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="E147" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="F147" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>280</v>
+        <v>266</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -23111,18 +23114,18 @@
         <v>0</v>
       </c>
       <c r="D148" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="E148" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="F148" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>281</v>
+        <v>267</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -23131,18 +23134,18 @@
         <v>0</v>
       </c>
       <c r="D149" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="E149" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="F149" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>282</v>
+        <v>268</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -23151,18 +23154,18 @@
         <v>0</v>
       </c>
       <c r="D150" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="E150" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="F150" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>283</v>
+        <v>269</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -23171,18 +23174,18 @@
         <v>0</v>
       </c>
       <c r="D151" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="E151" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="F151" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>284</v>
+        <v>270</v>
       </c>
       <c r="B152">
         <v>1.060816E-2</v>
@@ -23191,18 +23194,18 @@
         <v>9.1128700000000003E-3</v>
       </c>
       <c r="D152" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="E152" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="F152" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>285</v>
+        <v>271</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -23211,18 +23214,18 @@
         <v>0</v>
       </c>
       <c r="D153" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="E153" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="F153" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>286</v>
+        <v>272</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -23231,18 +23234,18 @@
         <v>0</v>
       </c>
       <c r="D154" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="E154" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="F154" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>287</v>
+        <v>273</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -23251,18 +23254,18 @@
         <v>0</v>
       </c>
       <c r="D155" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="E155" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="F155" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>288</v>
+        <v>274</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -23271,18 +23274,18 @@
         <v>0</v>
       </c>
       <c r="D156" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="E156" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="F156" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>289</v>
+        <v>275</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -23291,18 +23294,18 @@
         <v>0</v>
       </c>
       <c r="D157" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="E157" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="F157" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>290</v>
+        <v>276</v>
       </c>
       <c r="B158">
         <v>7.8722199999999992E-3</v>
@@ -23311,18 +23314,18 @@
         <v>6.7625799999999998E-3</v>
       </c>
       <c r="D158" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="E158" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="F158" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>291</v>
+        <v>277</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -23331,18 +23334,18 @@
         <v>0</v>
       </c>
       <c r="D159" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="E159" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="F159" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>292</v>
+        <v>278</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -23351,18 +23354,18 @@
         <v>0</v>
       </c>
       <c r="D160" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="E160" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="F160" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>293</v>
+        <v>279</v>
       </c>
       <c r="B161">
         <v>1.4590899999999999E-3</v>
@@ -23371,18 +23374,18 @@
         <v>1.2534200000000001E-3</v>
       </c>
       <c r="D161" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="E161" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="F161" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>294</v>
+        <v>280</v>
       </c>
       <c r="B162">
         <v>3.2085199999999999E-3</v>
@@ -23391,18 +23394,18 @@
         <v>2.75626E-3</v>
       </c>
       <c r="D162" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="E162" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="F162" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>295</v>
+        <v>281</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -23411,18 +23414,18 @@
         <v>0</v>
       </c>
       <c r="D163" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="E163" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="F163" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>296</v>
+        <v>282</v>
       </c>
       <c r="B164">
         <v>1.238363E-2</v>
@@ -23431,18 +23434,18 @@
         <v>1.0638079999999999E-2</v>
       </c>
       <c r="D164" t="s">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c r="E164" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="F164" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>297</v>
+        <v>283</v>
       </c>
       <c r="B165">
         <v>1.7608000000000001E-3</v>
@@ -23451,18 +23454,18 @@
         <v>1.5126E-3</v>
       </c>
       <c r="D165" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="E165" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="F165" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>298</v>
+        <v>284</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -23471,18 +23474,18 @@
         <v>0</v>
       </c>
       <c r="D166" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="E166" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="F166" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>299</v>
+        <v>285</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -23491,18 +23494,18 @@
         <v>0</v>
       </c>
       <c r="D167" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="E167" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="F167" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>300</v>
+        <v>286</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -23511,18 +23514,18 @@
         <v>0</v>
       </c>
       <c r="D168" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="E168" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="F168" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>301</v>
+        <v>287</v>
       </c>
       <c r="B169">
         <v>1.9576300000000001E-3</v>
@@ -23531,18 +23534,18 @@
         <v>1.68169E-3</v>
       </c>
       <c r="D169" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="E169" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="F169" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>302</v>
+        <v>288</v>
       </c>
       <c r="B170">
         <v>5.5338799999999997E-3</v>
@@ -23551,13 +23554,13 @@
         <v>4.7538399999999996E-3</v>
       </c>
       <c r="D170" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="E170" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="F170" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>
@@ -23577,15 +23580,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>303</v>
+        <v>289</v>
       </c>
       <c r="B1" t="s">
-        <v>304</v>
+        <v>290</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>305</v>
+        <v>291</v>
       </c>
       <c r="B2">
         <v>0.06</v>
@@ -23593,7 +23596,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>306</v>
+        <v>292</v>
       </c>
       <c r="B3">
         <v>0.23</v>
@@ -23601,15 +23604,15 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>307</v>
+        <v>293</v>
       </c>
       <c r="B4">
-        <v>4.8</v>
+        <v>4.9000000000000004</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>308</v>
+        <v>294</v>
       </c>
       <c r="B5">
         <v>1.5599999999999999E-2</v>
@@ -23617,7 +23620,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>309</v>
+        <v>295</v>
       </c>
       <c r="B6">
         <v>4.9700000000000001E-2</v>
@@ -23625,7 +23628,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>310</v>
+        <v>296</v>
       </c>
       <c r="B7">
         <v>8.2699999999999996E-2</v>
@@ -23633,7 +23636,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>311</v>
+        <v>297</v>
       </c>
       <c r="B8">
         <v>0.13639999999999999</v>
@@ -23641,7 +23644,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>312</v>
+        <v>298</v>
       </c>
       <c r="B9">
         <v>4.4111999999999998E-2</v>
@@ -23649,7 +23652,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>313</v>
+        <v>299</v>
       </c>
       <c r="B10">
         <v>3.9019999999999999E-2</v>
@@ -23657,7 +23660,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>314</v>
+        <v>300</v>
       </c>
       <c r="B11">
         <v>3.6070999999999999E-2</v>
@@ -23665,7 +23668,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>315</v>
+        <v>301</v>
       </c>
       <c r="B12">
         <v>3.4789E-2</v>
@@ -23673,7 +23676,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>316</v>
+        <v>302</v>
       </c>
       <c r="B13">
         <v>1.5599999999999999E-2</v>
@@ -23681,7 +23684,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>317</v>
+        <v>303</v>
       </c>
       <c r="B14">
         <v>3.7900000000000003E-2</v>
@@ -23689,7 +23692,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>318</v>
+        <v>304</v>
       </c>
       <c r="B15">
         <v>2.3525000000000001E-2</v>
@@ -23697,7 +23700,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>319</v>
+        <v>305</v>
       </c>
       <c r="B16">
         <v>1.9036000000000001E-2</v>
@@ -23705,7 +23708,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>320</v>
+        <v>306</v>
       </c>
       <c r="B17">
         <v>1.4713E-2</v>
@@ -23713,7 +23716,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>321</v>
+        <v>307</v>
       </c>
       <c r="B18">
         <v>5.0000000000000001E-3</v>
@@ -23721,7 +23724,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>322</v>
+        <v>308</v>
       </c>
       <c r="B19">
         <v>8.5000000000000006E-3</v>
@@ -23729,7 +23732,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>323</v>
+        <v>309</v>
       </c>
       <c r="B20">
         <v>1.0900000000000001</v>
@@ -23737,7 +23740,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>324</v>
+        <v>310</v>
       </c>
       <c r="B21">
         <v>9.2999999999999992E-3</v>
@@ -23745,7 +23748,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>325</v>
+        <v>311</v>
       </c>
       <c r="B22">
         <v>1.0093000000000001</v>
@@ -23753,7 +23756,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="B23">
         <v>8.3999999999999995E-3</v>
@@ -23761,7 +23764,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>327</v>
+        <v>313</v>
       </c>
       <c r="B24">
         <v>1.0093000000000001</v>
@@ -23769,7 +23772,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>328</v>
+        <v>314</v>
       </c>
       <c r="B25">
         <v>7.7087000000000003E-2</v>
@@ -23777,7 +23780,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>329</v>
+        <v>315</v>
       </c>
       <c r="B26">
         <v>7.1995000000000003E-2</v>
@@ -23785,7 +23788,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>330</v>
+        <v>316</v>
       </c>
       <c r="B27">
         <v>6.8468000000000001E-2</v>
@@ -23793,7 +23796,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>331</v>
+        <v>317</v>
       </c>
       <c r="B28">
         <v>6.7185999999999996E-2</v>
@@ -23801,7 +23804,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>332</v>
+        <v>318</v>
       </c>
       <c r="B29">
         <v>1.036</v>
@@ -23809,7 +23812,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>333</v>
+        <v>319</v>
       </c>
       <c r="B30">
         <v>1.074E-2</v>
@@ -23817,7 +23820,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>334</v>
+        <v>320</v>
       </c>
       <c r="B31">
         <v>0.06</v>

--- a/data/simuladores/simulador-tarifarios-gas/tarifarios_gas_natural_Tiago_Felicia.xlsx
+++ b/data/simuladores/simulador-tarifarios-gas/tarifarios_gas_natural_Tiago_Felicia.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tiago\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{475F71F8-5B44-4B18-96AD-91CBF36A1D0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{419F3F8E-60E4-4247-A74B-0260BDBFCC66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tarifas_Gas_Master" sheetId="1" r:id="rId1"/>
@@ -258,18 +258,9 @@
     <t>Iberdrola</t>
   </si>
   <si>
-    <t>Iberdrola | Plano Mais Casa Gás 16%</t>
-  </si>
-  <si>
     <t>https://www.iberdrola.pt/casa/energia/plano-mais-casa-gas</t>
   </si>
   <si>
-    <t>Iberdrola | Plano Mais Casa Gás | 17% FE ou DDC</t>
-  </si>
-  <si>
-    <t>Iberdrola | Plano Mais Casa Gás | 18% FE + DDC</t>
-  </si>
-  <si>
     <t>JafPlus</t>
   </si>
   <si>
@@ -1068,9 +1059,6 @@
     <t>Luzigás | Plano Gás</t>
   </si>
   <si>
-    <t>Goldenergy | ACP Gás</t>
-  </si>
-  <si>
     <t>Goldenergy | Tarifa Index Gas 100% Online</t>
   </si>
   <si>
@@ -1086,15 +1074,6 @@
     <t>G9 | Energia +| Gás | FE</t>
   </si>
   <si>
-    <t>Galp | Casa &amp; Estrada |Gás | (- 4% 1 energia s/DD)</t>
-  </si>
-  <si>
-    <t>Galp | Casa &amp; Estrada |Gás | (- 6% 1 energia c/DD ou 2 energias s/DD)</t>
-  </si>
-  <si>
-    <t>Galp | Casa &amp; Estrada |Gás | (- 8% 2 energias c/DD)</t>
-  </si>
-  <si>
     <t>Goldenergy  | Digital | Gás | DD+FE</t>
   </si>
   <si>
@@ -1108,6 +1087,27 @@
   </si>
   <si>
     <t>Goldenergy | Desconto ao Máximo | Gás</t>
+  </si>
+  <si>
+    <t>Galp | Casa &amp; Estrada | Gás | (- 4% 1 energia s/DD)</t>
+  </si>
+  <si>
+    <t>Galp | Casa &amp; Estrada | Gás | (- 6% 1 energia c/DD ou 2 energias s/DD)</t>
+  </si>
+  <si>
+    <t>Galp | Casa &amp; Estrada | Gás | (- 8% 2 energias c/DD)</t>
+  </si>
+  <si>
+    <t>Iberdrola | Plano Mais Casa | Gás | 16%</t>
+  </si>
+  <si>
+    <t>Iberdrola | Plano Mais Casa | Gás | 17% FE ou DDC</t>
+  </si>
+  <si>
+    <t>Iberdrola | Plano Mais Casa | Gás | 18% FE + DDC</t>
+  </si>
+  <si>
+    <t>Goldenergy | ACP | Gás</t>
   </si>
 </sst>
 </file>
@@ -1596,13 +1596,13 @@
         <v>16</v>
       </c>
       <c r="R1" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="S1" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="T1" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
@@ -3170,7 +3170,7 @@
         <v>43</v>
       </c>
       <c r="B38" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="C38" t="s">
         <v>51</v>
@@ -3214,7 +3214,7 @@
         <v>43</v>
       </c>
       <c r="B39" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="C39" t="s">
         <v>51</v>
@@ -3258,7 +3258,7 @@
         <v>43</v>
       </c>
       <c r="B40" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="C40" t="s">
         <v>51</v>
@@ -3302,7 +3302,7 @@
         <v>43</v>
       </c>
       <c r="B41" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="C41" t="s">
         <v>51</v>
@@ -3346,7 +3346,7 @@
         <v>56</v>
       </c>
       <c r="B42" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="D42" t="s">
         <v>19</v>
@@ -3382,13 +3382,13 @@
         <v>57</v>
       </c>
       <c r="Q42" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="R42">
         <v>3</v>
       </c>
       <c r="S42" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.25">
@@ -3396,7 +3396,7 @@
         <v>56</v>
       </c>
       <c r="B43" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="D43" t="s">
         <v>19</v>
@@ -3432,13 +3432,13 @@
         <v>57</v>
       </c>
       <c r="Q43" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="R43">
         <v>3</v>
       </c>
       <c r="S43" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.25">
@@ -3446,7 +3446,7 @@
         <v>56</v>
       </c>
       <c r="B44" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="D44" t="s">
         <v>19</v>
@@ -3482,13 +3482,13 @@
         <v>57</v>
       </c>
       <c r="Q44" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="R44">
         <v>3</v>
       </c>
       <c r="S44" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.25">
@@ -3496,7 +3496,7 @@
         <v>56</v>
       </c>
       <c r="B45" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="D45" t="s">
         <v>19</v>
@@ -3532,13 +3532,13 @@
         <v>57</v>
       </c>
       <c r="Q45" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="R45">
         <v>3</v>
       </c>
       <c r="S45" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
     </row>
     <row r="46" spans="1:20" x14ac:dyDescent="0.25">
@@ -3546,7 +3546,7 @@
         <v>56</v>
       </c>
       <c r="B46" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="D46" t="s">
         <v>19</v>
@@ -3582,7 +3582,7 @@
         <v>57</v>
       </c>
       <c r="Q46" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="T46">
         <v>1</v>
@@ -3593,7 +3593,7 @@
         <v>56</v>
       </c>
       <c r="B47" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="D47" t="s">
         <v>19</v>
@@ -3629,7 +3629,7 @@
         <v>57</v>
       </c>
       <c r="Q47" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="T47">
         <v>1</v>
@@ -3640,7 +3640,7 @@
         <v>56</v>
       </c>
       <c r="B48" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="D48" t="s">
         <v>19</v>
@@ -3676,7 +3676,7 @@
         <v>57</v>
       </c>
       <c r="Q48" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="T48">
         <v>1</v>
@@ -3687,7 +3687,7 @@
         <v>56</v>
       </c>
       <c r="B49" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="D49" t="s">
         <v>19</v>
@@ -3723,7 +3723,7 @@
         <v>57</v>
       </c>
       <c r="Q49" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="T49">
         <v>1</v>
@@ -3734,7 +3734,7 @@
         <v>56</v>
       </c>
       <c r="B50" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="D50" t="s">
         <v>19</v>
@@ -3776,13 +3776,13 @@
         <v>58</v>
       </c>
       <c r="Q50" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="R50">
         <v>3</v>
       </c>
       <c r="S50" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
     </row>
     <row r="51" spans="1:20" x14ac:dyDescent="0.25">
@@ -3790,7 +3790,7 @@
         <v>56</v>
       </c>
       <c r="B51" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="D51" t="s">
         <v>19</v>
@@ -3832,13 +3832,13 @@
         <v>58</v>
       </c>
       <c r="Q51" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="R51">
         <v>3</v>
       </c>
       <c r="S51" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
     </row>
     <row r="52" spans="1:20" x14ac:dyDescent="0.25">
@@ -3846,7 +3846,7 @@
         <v>56</v>
       </c>
       <c r="B52" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="D52" t="s">
         <v>19</v>
@@ -3888,13 +3888,13 @@
         <v>58</v>
       </c>
       <c r="Q52" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="R52">
         <v>3</v>
       </c>
       <c r="S52" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
     </row>
     <row r="53" spans="1:20" x14ac:dyDescent="0.25">
@@ -3902,7 +3902,7 @@
         <v>56</v>
       </c>
       <c r="B53" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="D53" t="s">
         <v>19</v>
@@ -3944,13 +3944,13 @@
         <v>58</v>
       </c>
       <c r="Q53" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="R53">
         <v>3</v>
       </c>
       <c r="S53" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
     </row>
     <row r="54" spans="1:20" x14ac:dyDescent="0.25">
@@ -3958,7 +3958,7 @@
         <v>56</v>
       </c>
       <c r="B54" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="D54" t="s">
         <v>19</v>
@@ -4000,13 +4000,13 @@
         <v>58</v>
       </c>
       <c r="Q54" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="R54">
         <v>3</v>
       </c>
       <c r="S54" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
     </row>
     <row r="55" spans="1:20" x14ac:dyDescent="0.25">
@@ -4014,7 +4014,7 @@
         <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="D55" t="s">
         <v>19</v>
@@ -4056,13 +4056,13 @@
         <v>58</v>
       </c>
       <c r="Q55" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="R55">
         <v>3</v>
       </c>
       <c r="S55" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
     </row>
     <row r="56" spans="1:20" x14ac:dyDescent="0.25">
@@ -4070,7 +4070,7 @@
         <v>56</v>
       </c>
       <c r="B56" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="D56" t="s">
         <v>19</v>
@@ -4112,13 +4112,13 @@
         <v>58</v>
       </c>
       <c r="Q56" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="R56">
         <v>3</v>
       </c>
       <c r="S56" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
     </row>
     <row r="57" spans="1:20" x14ac:dyDescent="0.25">
@@ -4126,7 +4126,7 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="D57" t="s">
         <v>19</v>
@@ -4168,13 +4168,13 @@
         <v>58</v>
       </c>
       <c r="Q57" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="R57">
         <v>3</v>
       </c>
       <c r="S57" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
     </row>
     <row r="58" spans="1:20" x14ac:dyDescent="0.25">
@@ -4182,7 +4182,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="D58" t="s">
         <v>19</v>
@@ -4218,7 +4218,7 @@
         <v>58</v>
       </c>
       <c r="Q58" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="T58">
         <v>1</v>
@@ -4229,7 +4229,7 @@
         <v>56</v>
       </c>
       <c r="B59" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="D59" t="s">
         <v>19</v>
@@ -4265,7 +4265,7 @@
         <v>58</v>
       </c>
       <c r="Q59" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="T59">
         <v>1</v>
@@ -4276,7 +4276,7 @@
         <v>56</v>
       </c>
       <c r="B60" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="D60" t="s">
         <v>19</v>
@@ -4312,7 +4312,7 @@
         <v>58</v>
       </c>
       <c r="Q60" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="T60">
         <v>1</v>
@@ -4323,7 +4323,7 @@
         <v>56</v>
       </c>
       <c r="B61" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="D61" t="s">
         <v>19</v>
@@ -4359,7 +4359,7 @@
         <v>58</v>
       </c>
       <c r="Q61" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="T61">
         <v>1</v>
@@ -4370,7 +4370,7 @@
         <v>56</v>
       </c>
       <c r="B62" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="D62" t="s">
         <v>19</v>
@@ -4406,7 +4406,7 @@
         <v>58</v>
       </c>
       <c r="Q62" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="T62">
         <v>1</v>
@@ -4417,7 +4417,7 @@
         <v>56</v>
       </c>
       <c r="B63" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="D63" t="s">
         <v>19</v>
@@ -4453,7 +4453,7 @@
         <v>58</v>
       </c>
       <c r="Q63" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="T63">
         <v>1</v>
@@ -4464,7 +4464,7 @@
         <v>56</v>
       </c>
       <c r="B64" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="D64" t="s">
         <v>19</v>
@@ -4500,7 +4500,7 @@
         <v>58</v>
       </c>
       <c r="Q64" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="T64">
         <v>1</v>
@@ -4511,7 +4511,7 @@
         <v>56</v>
       </c>
       <c r="B65" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="D65" t="s">
         <v>19</v>
@@ -4547,7 +4547,7 @@
         <v>58</v>
       </c>
       <c r="Q65" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="T65">
         <v>1</v>
@@ -4558,7 +4558,7 @@
         <v>56</v>
       </c>
       <c r="B66" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="D66" t="s">
         <v>19</v>
@@ -4597,7 +4597,7 @@
         <v>3</v>
       </c>
       <c r="S66" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
     </row>
     <row r="67" spans="1:20" x14ac:dyDescent="0.25">
@@ -4605,7 +4605,7 @@
         <v>56</v>
       </c>
       <c r="B67" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="D67" t="s">
         <v>19</v>
@@ -4644,7 +4644,7 @@
         <v>3</v>
       </c>
       <c r="S67" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
     </row>
     <row r="68" spans="1:20" x14ac:dyDescent="0.25">
@@ -4652,7 +4652,7 @@
         <v>56</v>
       </c>
       <c r="B68" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="D68" t="s">
         <v>19</v>
@@ -4696,7 +4696,7 @@
         <v>56</v>
       </c>
       <c r="B69" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="D69" t="s">
         <v>19</v>
@@ -4740,7 +4740,7 @@
         <v>56</v>
       </c>
       <c r="B70" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="D70" t="s">
         <v>52</v>
@@ -4781,7 +4781,7 @@
         <v>56</v>
       </c>
       <c r="B71" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="D71" t="s">
         <v>52</v>
@@ -4822,7 +4822,7 @@
         <v>56</v>
       </c>
       <c r="B72" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="D72" t="s">
         <v>52</v>
@@ -4863,7 +4863,7 @@
         <v>56</v>
       </c>
       <c r="B73" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="D73" t="s">
         <v>52</v>
@@ -4904,7 +4904,7 @@
         <v>56</v>
       </c>
       <c r="B74" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D74" t="s">
         <v>19</v>
@@ -4943,7 +4943,7 @@
         <v>3</v>
       </c>
       <c r="S74" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
     </row>
     <row r="75" spans="1:20" x14ac:dyDescent="0.25">
@@ -4951,7 +4951,7 @@
         <v>56</v>
       </c>
       <c r="B75" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D75" t="s">
         <v>19</v>
@@ -4990,7 +4990,7 @@
         <v>3</v>
       </c>
       <c r="S75" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
     </row>
     <row r="76" spans="1:20" x14ac:dyDescent="0.25">
@@ -4998,7 +4998,7 @@
         <v>56</v>
       </c>
       <c r="B76" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D76" t="s">
         <v>19</v>
@@ -5037,7 +5037,7 @@
         <v>3</v>
       </c>
       <c r="S76" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
     </row>
     <row r="77" spans="1:20" x14ac:dyDescent="0.25">
@@ -5045,7 +5045,7 @@
         <v>56</v>
       </c>
       <c r="B77" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D77" t="s">
         <v>19</v>
@@ -5084,7 +5084,7 @@
         <v>3</v>
       </c>
       <c r="S77" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
     </row>
     <row r="78" spans="1:20" x14ac:dyDescent="0.25">
@@ -5092,7 +5092,7 @@
         <v>56</v>
       </c>
       <c r="B78" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="D78" t="s">
         <v>19</v>
@@ -5136,7 +5136,7 @@
         <v>56</v>
       </c>
       <c r="B79" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="D79" t="s">
         <v>19</v>
@@ -5180,7 +5180,7 @@
         <v>56</v>
       </c>
       <c r="B80" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="D80" t="s">
         <v>19</v>
@@ -5224,7 +5224,7 @@
         <v>56</v>
       </c>
       <c r="B81" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="D81" t="s">
         <v>19</v>
@@ -5268,7 +5268,7 @@
         <v>62</v>
       </c>
       <c r="B82" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="D82" t="s">
         <v>19</v>
@@ -5315,7 +5315,7 @@
         <v>62</v>
       </c>
       <c r="B83" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="D83" t="s">
         <v>19</v>
@@ -5362,7 +5362,7 @@
         <v>62</v>
       </c>
       <c r="B84" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="D84" t="s">
         <v>19</v>
@@ -5409,7 +5409,7 @@
         <v>62</v>
       </c>
       <c r="B85" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="D85" t="s">
         <v>19</v>
@@ -5620,7 +5620,7 @@
         <v>65</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D90" t="s">
         <v>19</v>
@@ -5661,7 +5661,7 @@
         <v>65</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D91" t="s">
         <v>19</v>
@@ -5702,7 +5702,7 @@
         <v>65</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D92" t="s">
         <v>19</v>
@@ -5743,7 +5743,7 @@
         <v>65</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D93" t="s">
         <v>19</v>
@@ -5784,7 +5784,7 @@
         <v>65</v>
       </c>
       <c r="B94" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D94" t="s">
         <v>19</v>
@@ -5825,7 +5825,7 @@
         <v>65</v>
       </c>
       <c r="B95" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D95" t="s">
         <v>19</v>
@@ -5866,7 +5866,7 @@
         <v>65</v>
       </c>
       <c r="B96" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D96" t="s">
         <v>19</v>
@@ -5907,7 +5907,7 @@
         <v>65</v>
       </c>
       <c r="B97" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D97" t="s">
         <v>19</v>
@@ -5948,7 +5948,7 @@
         <v>65</v>
       </c>
       <c r="B98" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D98" t="s">
         <v>19</v>
@@ -5989,7 +5989,7 @@
         <v>65</v>
       </c>
       <c r="B99" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D99" t="s">
         <v>19</v>
@@ -6030,7 +6030,7 @@
         <v>65</v>
       </c>
       <c r="B100" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D100" t="s">
         <v>19</v>
@@ -6071,7 +6071,7 @@
         <v>65</v>
       </c>
       <c r="B101" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D101" t="s">
         <v>19</v>
@@ -6112,7 +6112,7 @@
         <v>65</v>
       </c>
       <c r="B102" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="D102" t="s">
         <v>52</v>
@@ -6153,7 +6153,7 @@
         <v>65</v>
       </c>
       <c r="B103" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="D103" t="s">
         <v>52</v>
@@ -6194,7 +6194,7 @@
         <v>65</v>
       </c>
       <c r="B104" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="D104" t="s">
         <v>52</v>
@@ -6235,7 +6235,7 @@
         <v>65</v>
       </c>
       <c r="B105" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="D105" t="s">
         <v>52</v>
@@ -6276,7 +6276,7 @@
         <v>70</v>
       </c>
       <c r="B106" t="s">
-        <v>343</v>
+        <v>356</v>
       </c>
       <c r="D106" t="s">
         <v>19</v>
@@ -6317,7 +6317,7 @@
         <v>70</v>
       </c>
       <c r="B107" t="s">
-        <v>343</v>
+        <v>356</v>
       </c>
       <c r="D107" t="s">
         <v>19</v>
@@ -6358,7 +6358,7 @@
         <v>70</v>
       </c>
       <c r="B108" t="s">
-        <v>343</v>
+        <v>356</v>
       </c>
       <c r="D108" t="s">
         <v>19</v>
@@ -6399,7 +6399,7 @@
         <v>70</v>
       </c>
       <c r="B109" t="s">
-        <v>343</v>
+        <v>356</v>
       </c>
       <c r="D109" t="s">
         <v>19</v>
@@ -6440,7 +6440,7 @@
         <v>70</v>
       </c>
       <c r="B110" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="D110" t="s">
         <v>19</v>
@@ -6481,7 +6481,7 @@
         <v>70</v>
       </c>
       <c r="B111" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="D111" t="s">
         <v>19</v>
@@ -6522,7 +6522,7 @@
         <v>70</v>
       </c>
       <c r="B112" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="D112" t="s">
         <v>19</v>
@@ -6563,7 +6563,7 @@
         <v>70</v>
       </c>
       <c r="B113" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="D113" t="s">
         <v>19</v>
@@ -6604,7 +6604,7 @@
         <v>70</v>
       </c>
       <c r="B114" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="D114" t="s">
         <v>19</v>
@@ -6645,7 +6645,7 @@
         <v>70</v>
       </c>
       <c r="B115" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="D115" t="s">
         <v>19</v>
@@ -6686,7 +6686,7 @@
         <v>70</v>
       </c>
       <c r="B116" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="D116" t="s">
         <v>19</v>
@@ -6727,7 +6727,7 @@
         <v>70</v>
       </c>
       <c r="B117" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="D117" t="s">
         <v>19</v>
@@ -6768,7 +6768,7 @@
         <v>70</v>
       </c>
       <c r="B118" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="D118" t="s">
         <v>19</v>
@@ -6809,7 +6809,7 @@
         <v>70</v>
       </c>
       <c r="B119" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="D119" t="s">
         <v>19</v>
@@ -6850,7 +6850,7 @@
         <v>70</v>
       </c>
       <c r="B120" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="D120" t="s">
         <v>19</v>
@@ -6891,7 +6891,7 @@
         <v>70</v>
       </c>
       <c r="B121" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="D121" t="s">
         <v>19</v>
@@ -6932,7 +6932,7 @@
         <v>70</v>
       </c>
       <c r="B122" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="D122" t="s">
         <v>19</v>
@@ -6973,7 +6973,7 @@
         <v>70</v>
       </c>
       <c r="B123" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="D123" t="s">
         <v>19</v>
@@ -7014,7 +7014,7 @@
         <v>70</v>
       </c>
       <c r="B124" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="D124" t="s">
         <v>19</v>
@@ -7055,7 +7055,7 @@
         <v>70</v>
       </c>
       <c r="B125" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="D125" t="s">
         <v>19</v>
@@ -7096,7 +7096,7 @@
         <v>70</v>
       </c>
       <c r="B126" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="D126" t="s">
         <v>19</v>
@@ -7137,7 +7137,7 @@
         <v>70</v>
       </c>
       <c r="B127" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="D127" t="s">
         <v>19</v>
@@ -7178,7 +7178,7 @@
         <v>70</v>
       </c>
       <c r="B128" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="D128" t="s">
         <v>19</v>
@@ -7219,7 +7219,7 @@
         <v>70</v>
       </c>
       <c r="B129" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="D129" t="s">
         <v>19</v>
@@ -7260,7 +7260,7 @@
         <v>70</v>
       </c>
       <c r="B130" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="D130" t="s">
         <v>52</v>
@@ -7301,7 +7301,7 @@
         <v>70</v>
       </c>
       <c r="B131" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="D131" t="s">
         <v>52</v>
@@ -7342,7 +7342,7 @@
         <v>70</v>
       </c>
       <c r="B132" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="D132" t="s">
         <v>52</v>
@@ -7383,7 +7383,7 @@
         <v>70</v>
       </c>
       <c r="B133" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="D133" t="s">
         <v>52</v>
@@ -7424,7 +7424,7 @@
         <v>72</v>
       </c>
       <c r="B134" t="s">
-        <v>73</v>
+        <v>353</v>
       </c>
       <c r="D134" t="s">
         <v>19</v>
@@ -7457,7 +7457,7 @@
         <v>24</v>
       </c>
       <c r="P134" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="135" spans="1:16" x14ac:dyDescent="0.25">
@@ -7465,7 +7465,7 @@
         <v>72</v>
       </c>
       <c r="B135" t="s">
-        <v>73</v>
+        <v>353</v>
       </c>
       <c r="D135" t="s">
         <v>19</v>
@@ -7498,7 +7498,7 @@
         <v>24</v>
       </c>
       <c r="P135" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="136" spans="1:16" x14ac:dyDescent="0.25">
@@ -7506,7 +7506,7 @@
         <v>72</v>
       </c>
       <c r="B136" t="s">
-        <v>73</v>
+        <v>353</v>
       </c>
       <c r="D136" t="s">
         <v>19</v>
@@ -7539,7 +7539,7 @@
         <v>24</v>
       </c>
       <c r="P136" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="137" spans="1:16" x14ac:dyDescent="0.25">
@@ -7547,7 +7547,7 @@
         <v>72</v>
       </c>
       <c r="B137" t="s">
-        <v>73</v>
+        <v>353</v>
       </c>
       <c r="D137" t="s">
         <v>19</v>
@@ -7580,7 +7580,7 @@
         <v>24</v>
       </c>
       <c r="P137" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="138" spans="1:16" x14ac:dyDescent="0.25">
@@ -7588,7 +7588,7 @@
         <v>72</v>
       </c>
       <c r="B138" t="s">
-        <v>75</v>
+        <v>354</v>
       </c>
       <c r="D138" t="s">
         <v>19</v>
@@ -7621,7 +7621,7 @@
         <v>24</v>
       </c>
       <c r="P138" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="139" spans="1:16" x14ac:dyDescent="0.25">
@@ -7629,7 +7629,7 @@
         <v>72</v>
       </c>
       <c r="B139" t="s">
-        <v>75</v>
+        <v>354</v>
       </c>
       <c r="D139" t="s">
         <v>19</v>
@@ -7662,7 +7662,7 @@
         <v>24</v>
       </c>
       <c r="P139" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="140" spans="1:16" x14ac:dyDescent="0.25">
@@ -7670,7 +7670,7 @@
         <v>72</v>
       </c>
       <c r="B140" t="s">
-        <v>75</v>
+        <v>354</v>
       </c>
       <c r="D140" t="s">
         <v>19</v>
@@ -7703,7 +7703,7 @@
         <v>24</v>
       </c>
       <c r="P140" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="141" spans="1:16" x14ac:dyDescent="0.25">
@@ -7711,7 +7711,7 @@
         <v>72</v>
       </c>
       <c r="B141" t="s">
-        <v>75</v>
+        <v>354</v>
       </c>
       <c r="D141" t="s">
         <v>19</v>
@@ -7744,7 +7744,7 @@
         <v>24</v>
       </c>
       <c r="P141" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="142" spans="1:16" x14ac:dyDescent="0.25">
@@ -7752,7 +7752,7 @@
         <v>72</v>
       </c>
       <c r="B142" t="s">
-        <v>76</v>
+        <v>355</v>
       </c>
       <c r="D142" t="s">
         <v>19</v>
@@ -7785,7 +7785,7 @@
         <v>24</v>
       </c>
       <c r="P142" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="143" spans="1:16" x14ac:dyDescent="0.25">
@@ -7793,7 +7793,7 @@
         <v>72</v>
       </c>
       <c r="B143" t="s">
-        <v>76</v>
+        <v>355</v>
       </c>
       <c r="D143" t="s">
         <v>19</v>
@@ -7826,7 +7826,7 @@
         <v>24</v>
       </c>
       <c r="P143" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="144" spans="1:16" x14ac:dyDescent="0.25">
@@ -7834,7 +7834,7 @@
         <v>72</v>
       </c>
       <c r="B144" t="s">
-        <v>76</v>
+        <v>355</v>
       </c>
       <c r="D144" t="s">
         <v>19</v>
@@ -7867,7 +7867,7 @@
         <v>24</v>
       </c>
       <c r="P144" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="145" spans="1:19" x14ac:dyDescent="0.25">
@@ -7875,7 +7875,7 @@
         <v>72</v>
       </c>
       <c r="B145" t="s">
-        <v>76</v>
+        <v>355</v>
       </c>
       <c r="D145" t="s">
         <v>19</v>
@@ -7908,15 +7908,15 @@
         <v>24</v>
       </c>
       <c r="P145" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="146" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B146" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D146" t="s">
         <v>19</v>
@@ -7949,15 +7949,15 @@
         <v>24</v>
       </c>
       <c r="P146" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="147" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B147" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D147" t="s">
         <v>19</v>
@@ -7990,15 +7990,15 @@
         <v>24</v>
       </c>
       <c r="P147" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="148" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B148" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D148" t="s">
         <v>19</v>
@@ -8031,15 +8031,15 @@
         <v>24</v>
       </c>
       <c r="P148" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="149" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B149" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D149" t="s">
         <v>19</v>
@@ -8072,15 +8072,15 @@
         <v>24</v>
       </c>
       <c r="P149" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="150" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B150" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="D150" t="s">
         <v>52</v>
@@ -8113,15 +8113,15 @@
         <v>54</v>
       </c>
       <c r="P150" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="151" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B151" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="D151" t="s">
         <v>52</v>
@@ -8154,15 +8154,15 @@
         <v>54</v>
       </c>
       <c r="P151" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="152" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B152" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="D152" t="s">
         <v>52</v>
@@ -8195,15 +8195,15 @@
         <v>54</v>
       </c>
       <c r="P152" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="153" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B153" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="D153" t="s">
         <v>52</v>
@@ -8236,15 +8236,15 @@
         <v>54</v>
       </c>
       <c r="P153" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="154" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B154" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="D154" t="s">
         <v>19</v>
@@ -8277,18 +8277,18 @@
         <v>24</v>
       </c>
       <c r="P154" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="S154" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="155" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B155" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="D155" t="s">
         <v>19</v>
@@ -8321,15 +8321,15 @@
         <v>24</v>
       </c>
       <c r="P155" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="156" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B156" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="D156" t="s">
         <v>19</v>
@@ -8362,15 +8362,15 @@
         <v>24</v>
       </c>
       <c r="P156" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="157" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B157" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="D157" t="s">
         <v>19</v>
@@ -8403,7 +8403,7 @@
         <v>24</v>
       </c>
       <c r="P157" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -8422,10 +8422,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -20131,15 +20131,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B2" s="1">
         <v>46184</v>
@@ -20165,19 +20165,19 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D1" t="s">
         <v>89</v>
       </c>
-      <c r="B1" t="s">
+      <c r="E1" t="s">
         <v>90</v>
-      </c>
-      <c r="C1" t="s">
-        <v>91</v>
-      </c>
-      <c r="D1" t="s">
-        <v>92</v>
-      </c>
-      <c r="E1" t="s">
-        <v>93</v>
       </c>
       <c r="F1" t="s">
         <v>15</v>
@@ -20185,7 +20185,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -20194,18 +20194,18 @@
         <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E2" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -20214,18 +20214,18 @@
         <v>0</v>
       </c>
       <c r="D3" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -20234,18 +20234,18 @@
         <v>0</v>
       </c>
       <c r="D4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E4" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F4" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -20254,18 +20254,18 @@
         <v>0</v>
       </c>
       <c r="D5" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E5" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F5" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -20274,18 +20274,18 @@
         <v>0</v>
       </c>
       <c r="D6" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F6" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -20294,18 +20294,18 @@
         <v>0</v>
       </c>
       <c r="D7" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E7" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="F7" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B8">
         <v>3.4684899999999999E-3</v>
@@ -20314,18 +20314,18 @@
         <v>2.9795799999999999E-3</v>
       </c>
       <c r="D8" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E8" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F8" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B9">
         <v>1.1611679999999999E-2</v>
@@ -20334,18 +20334,18 @@
         <v>9.9749399999999998E-3</v>
       </c>
       <c r="D9" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E9" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F9" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -20354,18 +20354,18 @@
         <v>0</v>
       </c>
       <c r="D10" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E10" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F10" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B11">
         <v>4.2528599999999998E-3</v>
@@ -20374,18 +20374,18 @@
         <v>3.6533899999999998E-3</v>
       </c>
       <c r="D11" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E11" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="F11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -20394,18 +20394,18 @@
         <v>0</v>
       </c>
       <c r="D12" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E12" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F12" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -20414,18 +20414,18 @@
         <v>0</v>
       </c>
       <c r="D13" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E13" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F13" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B14">
         <v>2.4159300000000002E-3</v>
@@ -20434,18 +20434,18 @@
         <v>2.0753899999999999E-3</v>
       </c>
       <c r="D14" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E14" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F14" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B15">
         <v>8.6965299999999992E-3</v>
@@ -20454,18 +20454,18 @@
         <v>7.4707000000000003E-3</v>
       </c>
       <c r="D15" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="E15" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F15" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -20474,18 +20474,18 @@
         <v>0</v>
       </c>
       <c r="D16" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E16" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F16" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -20494,18 +20494,18 @@
         <v>0</v>
       </c>
       <c r="D17" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E17" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F17" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -20514,18 +20514,18 @@
         <v>0</v>
       </c>
       <c r="D18" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E18" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F18" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B19">
         <v>1.28383E-2</v>
@@ -20534,18 +20534,18 @@
         <v>1.1028659999999999E-2</v>
       </c>
       <c r="D19" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E19" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F19" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B20">
         <v>4.3978699999999999E-3</v>
@@ -20554,18 +20554,18 @@
         <v>3.7779699999999999E-3</v>
       </c>
       <c r="D20" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E20" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F20" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B21">
         <v>7.07524E-3</v>
@@ -20574,18 +20574,18 @@
         <v>6.0779400000000004E-3</v>
       </c>
       <c r="D21" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E21" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F21" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -20594,18 +20594,18 @@
         <v>0</v>
       </c>
       <c r="D22" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E22" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F22" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B23">
         <v>4.7299999999999996E-6</v>
@@ -20614,18 +20614,18 @@
         <v>4.0600000000000001E-6</v>
       </c>
       <c r="D23" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E23" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F23" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B24">
         <v>3.0895679999999998E-2</v>
@@ -20634,18 +20634,18 @@
         <v>2.6540749999999998E-2</v>
       </c>
       <c r="D24" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E24" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="F24" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -20654,18 +20654,18 @@
         <v>0</v>
       </c>
       <c r="D25" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E25" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F25" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -20674,18 +20674,18 @@
         <v>0</v>
       </c>
       <c r="D26" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E26" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="F26" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -20694,18 +20694,18 @@
         <v>0</v>
       </c>
       <c r="D27" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E27" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="F27" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -20714,18 +20714,18 @@
         <v>0</v>
       </c>
       <c r="D28" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E28" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F28" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B29">
         <v>1.3180900000000001E-3</v>
@@ -20734,18 +20734,18 @@
         <v>1.13229E-3</v>
       </c>
       <c r="D29" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E29" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F29" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -20754,18 +20754,18 @@
         <v>0</v>
       </c>
       <c r="D30" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="E30" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F30" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -20774,18 +20774,18 @@
         <v>0</v>
       </c>
       <c r="D31" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E31" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F31" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -20794,18 +20794,18 @@
         <v>0</v>
       </c>
       <c r="D32" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E32" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F32" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -20814,18 +20814,18 @@
         <v>0</v>
       </c>
       <c r="D33" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E33" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F33" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -20834,18 +20834,18 @@
         <v>0</v>
       </c>
       <c r="D34" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E34" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F34" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -20854,18 +20854,18 @@
         <v>0</v>
       </c>
       <c r="D35" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E35" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F35" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -20874,18 +20874,18 @@
         <v>0</v>
       </c>
       <c r="D36" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E36" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F36" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -20894,18 +20894,18 @@
         <v>0</v>
       </c>
       <c r="D37" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E37" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F37" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B38">
         <v>1.6042899999999999E-2</v>
@@ -20914,18 +20914,18 @@
         <v>1.378155E-2</v>
       </c>
       <c r="D38" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E38" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F38" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B39">
         <v>1.6049600000000001E-2</v>
@@ -20934,18 +20934,18 @@
         <v>1.3787310000000001E-2</v>
       </c>
       <c r="D39" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E39" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F39" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -20954,18 +20954,18 @@
         <v>0</v>
       </c>
       <c r="D40" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E40" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="F40" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -20974,18 +20974,18 @@
         <v>0</v>
       </c>
       <c r="D41" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E41" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F41" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -20994,18 +20994,18 @@
         <v>0</v>
       </c>
       <c r="D42" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E42" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F42" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B43">
         <v>4.38719E-3</v>
@@ -21014,18 +21014,18 @@
         <v>3.7687900000000002E-3</v>
       </c>
       <c r="D43" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="E43" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F43" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B44">
         <v>5.8240699999999998E-3</v>
@@ -21034,18 +21034,18 @@
         <v>5.0031299999999997E-3</v>
       </c>
       <c r="D44" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E44" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F44" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B45">
         <v>5.0403100000000001E-3</v>
@@ -21054,18 +21054,18 @@
         <v>4.3298499999999997E-3</v>
       </c>
       <c r="D45" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E45" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F45" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -21074,18 +21074,18 @@
         <v>0</v>
       </c>
       <c r="D46" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E46" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F46" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -21094,18 +21094,18 @@
         <v>0</v>
       </c>
       <c r="D47" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E47" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F47" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -21114,18 +21114,18 @@
         <v>0</v>
       </c>
       <c r="D48" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E48" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="F48" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -21134,18 +21134,18 @@
         <v>0</v>
       </c>
       <c r="D49" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E49" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F49" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -21154,18 +21154,18 @@
         <v>0</v>
       </c>
       <c r="D50" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E50" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F50" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -21174,18 +21174,18 @@
         <v>0</v>
       </c>
       <c r="D51" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E51" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F51" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B52">
         <v>1.609E-5</v>
@@ -21194,18 +21194,18 @@
         <v>1.382E-5</v>
       </c>
       <c r="D52" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E52" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F52" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B53">
         <v>6.5729200000000003E-3</v>
@@ -21214,18 +21214,18 @@
         <v>5.64643E-3</v>
       </c>
       <c r="D53" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E53" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F53" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B54">
         <v>1.8657730000000001E-2</v>
@@ -21234,18 +21234,18 @@
         <v>1.602781E-2</v>
       </c>
       <c r="D54" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E54" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="F54" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="B55">
         <v>1.6368299999999999E-3</v>
@@ -21254,18 +21254,18 @@
         <v>1.4061099999999999E-3</v>
       </c>
       <c r="D55" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E55" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F55" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -21274,18 +21274,18 @@
         <v>0</v>
       </c>
       <c r="D56" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="E56" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="F56" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -21294,18 +21294,18 @@
         <v>0</v>
       </c>
       <c r="D57" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E57" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F57" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B58">
         <v>1.541E-5</v>
@@ -21314,18 +21314,18 @@
         <v>1.324E-5</v>
       </c>
       <c r="D58" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E58" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F58" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -21334,18 +21334,18 @@
         <v>0</v>
       </c>
       <c r="D59" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E59" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F59" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="B60">
         <v>2.8363300000000002E-3</v>
@@ -21354,18 +21354,18 @@
         <v>2.4365300000000001E-3</v>
       </c>
       <c r="D60" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E60" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="F60" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -21374,18 +21374,18 @@
         <v>0</v>
       </c>
       <c r="D61" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E61" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F61" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="B62">
         <v>9.9309000000000008E-4</v>
@@ -21394,18 +21394,18 @@
         <v>8.5309999999999997E-4</v>
       </c>
       <c r="D62" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E62" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F62" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -21414,18 +21414,18 @@
         <v>0</v>
       </c>
       <c r="D63" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E63" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="F63" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B64">
         <v>3.8569099999999999E-3</v>
@@ -21434,18 +21434,18 @@
         <v>3.3132600000000002E-3</v>
       </c>
       <c r="D64" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E64" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F64" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -21454,18 +21454,18 @@
         <v>0</v>
       </c>
       <c r="D65" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E65" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F65" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B66">
         <v>5.8233699999999996E-3</v>
@@ -21474,18 +21474,18 @@
         <v>5.0025299999999998E-3</v>
       </c>
       <c r="D66" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E66" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="F66" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -21494,18 +21494,18 @@
         <v>0</v>
       </c>
       <c r="D67" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E67" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F67" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B68">
         <v>4.4916699999999997E-3</v>
@@ -21514,18 +21514,18 @@
         <v>3.8585500000000001E-3</v>
       </c>
       <c r="D68" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E68" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F68" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B69">
         <v>7.0537899999999999E-3</v>
@@ -21534,18 +21534,18 @@
         <v>6.0595099999999997E-3</v>
       </c>
       <c r="D69" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E69" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F69" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B70">
         <v>1.0788590000000001E-2</v>
@@ -21554,18 +21554,18 @@
         <v>9.2678799999999992E-3</v>
       </c>
       <c r="D70" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E70" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="F70" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -21574,18 +21574,18 @@
         <v>0</v>
       </c>
       <c r="D71" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E71" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F71" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -21594,18 +21594,18 @@
         <v>0</v>
       </c>
       <c r="D72" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E72" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F72" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B73">
         <v>4.2203800000000001E-3</v>
@@ -21614,18 +21614,18 @@
         <v>3.6254899999999999E-3</v>
       </c>
       <c r="D73" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E73" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F73" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="B74">
         <v>6.9173799999999999E-3</v>
@@ -21634,18 +21634,18 @@
         <v>5.94233E-3</v>
       </c>
       <c r="D74" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E74" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F74" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -21654,18 +21654,18 @@
         <v>0</v>
       </c>
       <c r="D75" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E75" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="F75" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B76">
         <v>0</v>
@@ -21674,18 +21674,18 @@
         <v>0</v>
       </c>
       <c r="D76" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="E76" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F76" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B77">
         <v>0</v>
@@ -21694,18 +21694,18 @@
         <v>0</v>
       </c>
       <c r="D77" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E77" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F77" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B78">
         <v>5.3032499999999998E-3</v>
@@ -21714,18 +21714,18 @@
         <v>4.5557200000000001E-3</v>
       </c>
       <c r="D78" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E78" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F78" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -21734,18 +21734,18 @@
         <v>0</v>
       </c>
       <c r="D79" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E79" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F79" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -21754,18 +21754,18 @@
         <v>0</v>
       </c>
       <c r="D80" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E80" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F80" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -21774,18 +21774,18 @@
         <v>0</v>
       </c>
       <c r="D81" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E81" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F81" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -21794,18 +21794,18 @@
         <v>0</v>
       </c>
       <c r="D82" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E82" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="F82" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -21814,18 +21814,18 @@
         <v>0</v>
       </c>
       <c r="D83" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E83" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F83" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="B84">
         <v>3.19002E-3</v>
@@ -21834,18 +21834,18 @@
         <v>2.7403699999999998E-3</v>
       </c>
       <c r="D84" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E84" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F84" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -21854,18 +21854,18 @@
         <v>0</v>
       </c>
       <c r="D85" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E85" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F85" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B86">
         <v>1.4809839999999999E-2</v>
@@ -21874,18 +21874,18 @@
         <v>1.2722300000000001E-2</v>
       </c>
       <c r="D86" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E86" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="F86" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -21894,18 +21894,18 @@
         <v>0</v>
       </c>
       <c r="D87" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E87" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F87" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -21914,18 +21914,18 @@
         <v>0</v>
       </c>
       <c r="D88" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E88" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F88" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -21934,18 +21934,18 @@
         <v>0</v>
       </c>
       <c r="D89" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E89" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F89" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -21954,18 +21954,18 @@
         <v>0</v>
       </c>
       <c r="D90" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E90" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F90" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="B91">
         <v>1.6499100000000001E-3</v>
@@ -21974,18 +21974,18 @@
         <v>1.4173499999999999E-3</v>
       </c>
       <c r="D91" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E91" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="F91" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -21994,18 +21994,18 @@
         <v>0</v>
       </c>
       <c r="D92" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E92" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="F92" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -22014,18 +22014,18 @@
         <v>0</v>
       </c>
       <c r="D93" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E93" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F93" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -22034,18 +22034,18 @@
         <v>0</v>
       </c>
       <c r="D94" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E94" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F94" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -22054,18 +22054,18 @@
         <v>0</v>
       </c>
       <c r="D95" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E95" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F95" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -22074,18 +22074,18 @@
         <v>0</v>
       </c>
       <c r="D96" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E96" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="F96" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -22094,18 +22094,18 @@
         <v>0</v>
       </c>
       <c r="D97" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E97" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F97" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B98">
         <v>9.1582199999999999E-3</v>
@@ -22114,18 +22114,18 @@
         <v>7.8673100000000006E-3</v>
       </c>
       <c r="D98" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E98" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F98" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B99">
         <v>6.67637E-3</v>
@@ -22134,18 +22134,18 @@
         <v>5.7352999999999996E-3</v>
       </c>
       <c r="D99" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E99" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F99" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -22154,18 +22154,18 @@
         <v>0</v>
       </c>
       <c r="D100" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="E100" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="F100" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -22174,18 +22174,18 @@
         <v>0</v>
       </c>
       <c r="D101" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E101" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F101" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -22194,18 +22194,18 @@
         <v>0</v>
       </c>
       <c r="D102" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E102" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F102" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -22214,18 +22214,18 @@
         <v>0</v>
       </c>
       <c r="D103" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E103" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="F103" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -22234,18 +22234,18 @@
         <v>0</v>
       </c>
       <c r="D104" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E104" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F104" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="B105">
         <v>5.6688900000000002E-3</v>
@@ -22254,18 +22254,18 @@
         <v>4.8698300000000003E-3</v>
       </c>
       <c r="D105" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E105" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F105" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="B106">
         <v>3.3768100000000001E-3</v>
@@ -22274,18 +22274,18 @@
         <v>2.9008300000000001E-3</v>
       </c>
       <c r="D106" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E106" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F106" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="B107">
         <v>4.6591799999999997E-3</v>
@@ -22294,18 +22294,18 @@
         <v>4.0024400000000003E-3</v>
       </c>
       <c r="D107" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E107" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="F107" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B108">
         <v>1.9069499999999999E-3</v>
@@ -22314,18 +22314,18 @@
         <v>1.6381600000000001E-3</v>
       </c>
       <c r="D108" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E108" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F108" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -22334,18 +22334,18 @@
         <v>0</v>
       </c>
       <c r="D109" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E109" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F109" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="B110">
         <v>5.3588300000000002E-3</v>
@@ -22354,18 +22354,18 @@
         <v>4.6034700000000001E-3</v>
       </c>
       <c r="D110" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E110" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F110" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -22374,18 +22374,18 @@
         <v>0</v>
       </c>
       <c r="D111" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E111" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F111" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="B112">
         <v>3.2703900000000002E-3</v>
@@ -22394,18 +22394,18 @@
         <v>2.80941E-3</v>
       </c>
       <c r="D112" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E112" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F112" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -22414,18 +22414,18 @@
         <v>0</v>
       </c>
       <c r="D113" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E113" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F113" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B114">
         <v>0</v>
@@ -22434,18 +22434,18 @@
         <v>0</v>
       </c>
       <c r="D114" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E114" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F114" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B115">
         <v>0</v>
@@ -22454,18 +22454,18 @@
         <v>0</v>
       </c>
       <c r="D115" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E115" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F115" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="B116">
         <v>0</v>
@@ -22474,18 +22474,18 @@
         <v>0</v>
       </c>
       <c r="D116" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E116" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F116" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="B117">
         <v>0</v>
@@ -22494,18 +22494,18 @@
         <v>0</v>
       </c>
       <c r="D117" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E117" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F117" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B118">
         <v>4.0392600000000002E-3</v>
@@ -22514,18 +22514,18 @@
         <v>3.4699000000000002E-3</v>
       </c>
       <c r="D118" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="E118" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="F118" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B119">
         <v>2.1069499999999998E-3</v>
@@ -22534,18 +22534,18 @@
         <v>1.80996E-3</v>
       </c>
       <c r="D119" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E119" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F119" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="B120">
         <v>0</v>
@@ -22554,18 +22554,18 @@
         <v>0</v>
       </c>
       <c r="D120" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E120" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F120" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="B121">
         <v>0</v>
@@ -22574,18 +22574,18 @@
         <v>0</v>
       </c>
       <c r="D121" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E121" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F121" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B122">
         <v>8.9892199999999992E-3</v>
@@ -22594,18 +22594,18 @@
         <v>7.7221399999999997E-3</v>
       </c>
       <c r="D122" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E122" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F122" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="B123">
         <v>0</v>
@@ -22614,18 +22614,18 @@
         <v>0</v>
       </c>
       <c r="D123" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E123" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F123" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B124">
         <v>0</v>
@@ -22634,18 +22634,18 @@
         <v>0</v>
       </c>
       <c r="D124" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E124" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F124" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B125">
         <v>0</v>
@@ -22654,18 +22654,18 @@
         <v>0</v>
       </c>
       <c r="D125" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E125" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F125" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="B126">
         <v>0</v>
@@ -22674,18 +22674,18 @@
         <v>0</v>
       </c>
       <c r="D126" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E126" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F126" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B127">
         <v>0</v>
@@ -22694,18 +22694,18 @@
         <v>0</v>
       </c>
       <c r="D127" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E127" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="F127" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="B128">
         <v>2.1070799999999999E-3</v>
@@ -22714,18 +22714,18 @@
         <v>1.81007E-3</v>
       </c>
       <c r="D128" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E128" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F128" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="B129">
         <v>0</v>
@@ -22734,18 +22734,18 @@
         <v>0</v>
       </c>
       <c r="D129" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E129" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F129" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B130">
         <v>6.0648300000000002E-3</v>
@@ -22754,18 +22754,18 @@
         <v>5.2099599999999996E-3</v>
       </c>
       <c r="D130" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E130" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F130" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="B131">
         <v>6.4330799999999999E-3</v>
@@ -22774,18 +22774,18 @@
         <v>5.5262999999999996E-3</v>
       </c>
       <c r="D131" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E131" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F131" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="B132">
         <v>0</v>
@@ -22794,18 +22794,18 @@
         <v>0</v>
       </c>
       <c r="D132" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E132" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="F132" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B133">
         <v>0</v>
@@ -22814,18 +22814,18 @@
         <v>0</v>
       </c>
       <c r="D133" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E133" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="F133" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="B134">
         <v>1.27568E-2</v>
@@ -22834,18 +22834,18 @@
         <v>1.095865E-2</v>
       </c>
       <c r="D134" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E134" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="F134" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="B135">
         <v>0</v>
@@ -22854,18 +22854,18 @@
         <v>0</v>
       </c>
       <c r="D135" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E135" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="F135" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B136">
         <v>0</v>
@@ -22874,18 +22874,18 @@
         <v>0</v>
       </c>
       <c r="D136" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E136" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="F136" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="B137">
         <v>1.0773E-2</v>
@@ -22894,18 +22894,18 @@
         <v>9.2544800000000007E-3</v>
       </c>
       <c r="D137" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E137" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="F137" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="B138">
         <v>1.21697E-2</v>
@@ -22914,18 +22914,18 @@
         <v>1.04543E-2</v>
       </c>
       <c r="D138" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E138" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F138" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -22934,18 +22934,18 @@
         <v>0</v>
       </c>
       <c r="D139" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E139" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F139" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -22954,18 +22954,18 @@
         <v>0</v>
       </c>
       <c r="D140" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E140" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F140" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -22974,18 +22974,18 @@
         <v>0</v>
       </c>
       <c r="D141" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E141" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F141" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -22994,18 +22994,18 @@
         <v>0</v>
       </c>
       <c r="D142" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E142" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F142" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -23014,18 +23014,18 @@
         <v>0</v>
       </c>
       <c r="D143" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E143" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F143" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -23034,18 +23034,18 @@
         <v>0</v>
       </c>
       <c r="D144" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E144" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="F144" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -23054,18 +23054,18 @@
         <v>0</v>
       </c>
       <c r="D145" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E145" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F145" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B146">
         <v>6.8610999999999998E-4</v>
@@ -23074,18 +23074,18 @@
         <v>5.8940000000000002E-4</v>
       </c>
       <c r="D146" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E146" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F146" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="B147">
         <v>1.174541E-2</v>
@@ -23094,18 +23094,18 @@
         <v>1.0089829999999999E-2</v>
       </c>
       <c r="D147" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E147" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F147" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -23114,18 +23114,18 @@
         <v>0</v>
       </c>
       <c r="D148" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E148" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F148" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -23134,18 +23134,18 @@
         <v>0</v>
       </c>
       <c r="D149" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E149" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F149" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -23154,18 +23154,18 @@
         <v>0</v>
       </c>
       <c r="D150" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E150" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F150" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -23174,18 +23174,18 @@
         <v>0</v>
       </c>
       <c r="D151" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E151" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F151" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="B152">
         <v>1.060816E-2</v>
@@ -23194,18 +23194,18 @@
         <v>9.1128700000000003E-3</v>
       </c>
       <c r="D152" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E152" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F152" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -23214,18 +23214,18 @@
         <v>0</v>
       </c>
       <c r="D153" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E153" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F153" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -23234,18 +23234,18 @@
         <v>0</v>
       </c>
       <c r="D154" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E154" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F154" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -23254,18 +23254,18 @@
         <v>0</v>
       </c>
       <c r="D155" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E155" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F155" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -23274,18 +23274,18 @@
         <v>0</v>
       </c>
       <c r="D156" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E156" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F156" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -23294,18 +23294,18 @@
         <v>0</v>
       </c>
       <c r="D157" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E157" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F157" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="B158">
         <v>7.8722199999999992E-3</v>
@@ -23314,18 +23314,18 @@
         <v>6.7625799999999998E-3</v>
       </c>
       <c r="D158" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E158" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F158" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -23334,18 +23334,18 @@
         <v>0</v>
       </c>
       <c r="D159" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E159" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F159" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -23354,18 +23354,18 @@
         <v>0</v>
       </c>
       <c r="D160" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E160" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F160" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="B161">
         <v>1.4590899999999999E-3</v>
@@ -23374,18 +23374,18 @@
         <v>1.2534200000000001E-3</v>
       </c>
       <c r="D161" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E161" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F161" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="B162">
         <v>3.2085199999999999E-3</v>
@@ -23394,18 +23394,18 @@
         <v>2.75626E-3</v>
       </c>
       <c r="D162" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E162" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F162" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -23414,18 +23414,18 @@
         <v>0</v>
       </c>
       <c r="D163" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E163" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F163" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="B164">
         <v>1.238363E-2</v>
@@ -23434,18 +23434,18 @@
         <v>1.0638079999999999E-2</v>
       </c>
       <c r="D164" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="E164" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F164" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="B165">
         <v>1.7608000000000001E-3</v>
@@ -23454,18 +23454,18 @@
         <v>1.5126E-3</v>
       </c>
       <c r="D165" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E165" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="F165" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -23474,18 +23474,18 @@
         <v>0</v>
       </c>
       <c r="D166" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E166" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F166" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -23494,18 +23494,18 @@
         <v>0</v>
       </c>
       <c r="D167" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E167" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F167" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -23514,18 +23514,18 @@
         <v>0</v>
       </c>
       <c r="D168" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E168" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F168" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B169">
         <v>1.9576300000000001E-3</v>
@@ -23534,18 +23534,18 @@
         <v>1.68169E-3</v>
       </c>
       <c r="D169" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E169" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="F169" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="B170">
         <v>5.5338799999999997E-3</v>
@@ -23554,13 +23554,13 @@
         <v>4.7538399999999996E-3</v>
       </c>
       <c r="D170" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E170" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F170" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -23580,15 +23580,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="B1" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="B2">
         <v>0.06</v>
@@ -23596,7 +23596,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="B3">
         <v>0.23</v>
@@ -23604,7 +23604,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="B4">
         <v>4.9000000000000004</v>
@@ -23612,7 +23612,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="B5">
         <v>1.5599999999999999E-2</v>
@@ -23620,7 +23620,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="B6">
         <v>4.9700000000000001E-2</v>
@@ -23628,7 +23628,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="B7">
         <v>8.2699999999999996E-2</v>
@@ -23636,7 +23636,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="B8">
         <v>0.13639999999999999</v>
@@ -23644,7 +23644,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="B9">
         <v>4.4111999999999998E-2</v>
@@ -23652,7 +23652,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="B10">
         <v>3.9019999999999999E-2</v>
@@ -23660,7 +23660,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="B11">
         <v>3.6070999999999999E-2</v>
@@ -23668,7 +23668,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="B12">
         <v>3.4789E-2</v>
@@ -23676,7 +23676,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="B13">
         <v>1.5599999999999999E-2</v>
@@ -23684,7 +23684,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="B14">
         <v>3.7900000000000003E-2</v>
@@ -23692,7 +23692,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="B15">
         <v>2.3525000000000001E-2</v>
@@ -23700,7 +23700,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="B16">
         <v>1.9036000000000001E-2</v>
@@ -23708,7 +23708,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="B17">
         <v>1.4713E-2</v>
@@ -23716,7 +23716,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="B18">
         <v>5.0000000000000001E-3</v>
@@ -23724,7 +23724,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="B19">
         <v>8.5000000000000006E-3</v>
@@ -23732,7 +23732,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="B20">
         <v>1.0900000000000001</v>
@@ -23740,7 +23740,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="B21">
         <v>9.2999999999999992E-3</v>
@@ -23748,7 +23748,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="B22">
         <v>1.0093000000000001</v>
@@ -23756,7 +23756,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="B23">
         <v>8.3999999999999995E-3</v>
@@ -23764,7 +23764,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B24">
         <v>1.0093000000000001</v>
@@ -23772,7 +23772,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="B25">
         <v>7.7087000000000003E-2</v>
@@ -23780,7 +23780,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="B26">
         <v>7.1995000000000003E-2</v>
@@ -23788,7 +23788,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="B27">
         <v>6.8468000000000001E-2</v>
@@ -23796,7 +23796,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="B28">
         <v>6.7185999999999996E-2</v>
@@ -23804,7 +23804,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="B29">
         <v>1.036</v>
@@ -23812,7 +23812,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="B30">
         <v>1.074E-2</v>
@@ -23820,7 +23820,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="B31">
         <v>0.06</v>

--- a/data/simuladores/simulador-tarifarios-gas/tarifarios_gas_natural_Tiago_Felicia.xlsx
+++ b/data/simuladores/simulador-tarifarios-gas/tarifarios_gas_natural_Tiago_Felicia.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tiago\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14C69DDC-6163-4F6F-AD36-93AA858B4D20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30C5103E-8DFB-4170-8FC4-FFAE1385B491}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tarifas_Gas_Master" sheetId="1" r:id="rId1"/>
@@ -1095,9 +1095,6 @@
     <t>https://www.endesa.pt/particulares/planos/gas/simples-gas</t>
   </si>
   <si>
-    <t>Endesa | Tarifa Indexada | Gás | Plano Amigo</t>
-  </si>
-  <si>
     <t>Endesa | Digital | Gás · (-20%) | Plano Amigo | DD + FE</t>
   </si>
   <si>
@@ -1120,6 +1117,9 @@
   </si>
   <si>
     <t>Galp | Plano COMBINA | Gás Natural</t>
+  </si>
+  <si>
+    <t>Endesa | Tarifa Indexada | Gás</t>
   </si>
 </sst>
 </file>
@@ -3631,7 +3631,7 @@
         <v>46</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D50" s="7" t="s">
         <v>19</v>
@@ -3678,7 +3678,7 @@
         <v>46</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D51" s="7" t="s">
         <v>19</v>
@@ -3725,7 +3725,7 @@
         <v>46</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D52" s="7" t="s">
         <v>19</v>
@@ -3772,7 +3772,7 @@
         <v>46</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D53" s="7" t="s">
         <v>19</v>
@@ -3819,7 +3819,7 @@
         <v>46</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D54" s="7" t="s">
         <v>19</v>
@@ -3870,7 +3870,7 @@
         <v>3</v>
       </c>
       <c r="X54" s="7" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="55" spans="1:25" s="7" customFormat="1" x14ac:dyDescent="0.35">
@@ -3878,7 +3878,7 @@
         <v>46</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D55" s="7" t="s">
         <v>19</v>
@@ -3929,7 +3929,7 @@
         <v>3</v>
       </c>
       <c r="X55" s="7" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="56" spans="1:25" s="7" customFormat="1" x14ac:dyDescent="0.35">
@@ -3937,7 +3937,7 @@
         <v>46</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D56" s="7" t="s">
         <v>19</v>
@@ -3988,7 +3988,7 @@
         <v>3</v>
       </c>
       <c r="X56" s="7" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="57" spans="1:25" s="7" customFormat="1" x14ac:dyDescent="0.35">
@@ -3996,7 +3996,7 @@
         <v>46</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D57" s="7" t="s">
         <v>19</v>
@@ -4047,7 +4047,7 @@
         <v>3</v>
       </c>
       <c r="X57" s="7" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="58" spans="1:25" s="7" customFormat="1" x14ac:dyDescent="0.35">
@@ -4055,7 +4055,7 @@
         <v>46</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D58" s="7" t="s">
         <v>19</v>
@@ -4111,7 +4111,7 @@
         <v>46</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D59" s="7" t="s">
         <v>19</v>
@@ -4167,7 +4167,7 @@
         <v>46</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D60" s="7" t="s">
         <v>19</v>
@@ -4223,7 +4223,7 @@
         <v>46</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D61" s="7" t="s">
         <v>19</v>
@@ -4279,7 +4279,7 @@
         <v>46</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D62" s="7" t="s">
         <v>19</v>
@@ -4330,7 +4330,7 @@
         <v>3</v>
       </c>
       <c r="X62" s="7" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="63" spans="1:25" s="7" customFormat="1" x14ac:dyDescent="0.35">
@@ -4338,7 +4338,7 @@
         <v>46</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D63" s="7" t="s">
         <v>19</v>
@@ -4389,7 +4389,7 @@
         <v>3</v>
       </c>
       <c r="X63" s="7" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="64" spans="1:25" s="7" customFormat="1" x14ac:dyDescent="0.35">
@@ -4397,7 +4397,7 @@
         <v>46</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D64" s="7" t="s">
         <v>19</v>
@@ -4448,7 +4448,7 @@
         <v>3</v>
       </c>
       <c r="X64" s="7" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="65" spans="1:25" s="7" customFormat="1" x14ac:dyDescent="0.35">
@@ -4456,7 +4456,7 @@
         <v>46</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D65" s="7" t="s">
         <v>19</v>
@@ -4507,7 +4507,7 @@
         <v>3</v>
       </c>
       <c r="X65" s="7" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="66" spans="1:25" s="7" customFormat="1" x14ac:dyDescent="0.35">
@@ -4515,7 +4515,7 @@
         <v>46</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D66" s="7" t="s">
         <v>19</v>
@@ -4571,7 +4571,7 @@
         <v>46</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D67" s="7" t="s">
         <v>19</v>
@@ -4627,7 +4627,7 @@
         <v>46</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D68" s="7" t="s">
         <v>19</v>
@@ -4683,7 +4683,7 @@
         <v>46</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D69" s="7" t="s">
         <v>19</v>
@@ -4739,7 +4739,7 @@
         <v>46</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D70" s="7" t="s">
         <v>19</v>
@@ -4783,7 +4783,7 @@
         <v>46</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D71" s="7" t="s">
         <v>19</v>
@@ -4827,7 +4827,7 @@
         <v>46</v>
       </c>
       <c r="B72" s="7" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="D72" s="7" t="s">
         <v>42</v>
@@ -4871,7 +4871,7 @@
         <v>46</v>
       </c>
       <c r="B73" s="7" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="D73" s="7" t="s">
         <v>42</v>
@@ -4915,7 +4915,7 @@
         <v>46</v>
       </c>
       <c r="B74" s="7" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="D74" s="7" t="s">
         <v>42</v>
@@ -4959,7 +4959,7 @@
         <v>46</v>
       </c>
       <c r="B75" s="7" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="D75" s="7" t="s">
         <v>42</v>
@@ -5003,7 +5003,7 @@
         <v>46</v>
       </c>
       <c r="B76" s="7" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D76" s="7" t="s">
         <v>19</v>
@@ -5050,7 +5050,7 @@
         <v>46</v>
       </c>
       <c r="B77" s="7" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D77" s="7" t="s">
         <v>19</v>
@@ -5097,7 +5097,7 @@
         <v>46</v>
       </c>
       <c r="B78" s="7" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D78" s="7" t="s">
         <v>19</v>
@@ -5144,7 +5144,7 @@
         <v>46</v>
       </c>
       <c r="B79" s="7" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D79" s="7" t="s">
         <v>19</v>
@@ -5191,7 +5191,7 @@
         <v>51</v>
       </c>
       <c r="B80" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D80" t="s">
         <v>19</v>
@@ -5233,7 +5233,7 @@
         <v>51</v>
       </c>
       <c r="B81" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D81" t="s">
         <v>19</v>
@@ -5275,7 +5275,7 @@
         <v>51</v>
       </c>
       <c r="B82" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D82" t="s">
         <v>19</v>
@@ -5317,7 +5317,7 @@
         <v>51</v>
       </c>
       <c r="B83" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D83" t="s">
         <v>19</v>

--- a/data/simuladores/simulador-tarifarios-gas/tarifarios_gas_natural_Tiago_Felicia.xlsx
+++ b/data/simuladores/simulador-tarifarios-gas/tarifarios_gas_natural_Tiago_Felicia.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tiago\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47C9806E-8FF4-41CD-A2D7-5B90430A5839}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF82E599-A2E3-46C4-8217-087EDA53F8C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tarifas_Gas_Master" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,9 @@
     <sheet name="TOS" sheetId="4" r:id="rId4"/>
     <sheet name="Constantes" sheetId="5" r:id="rId5"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Tarifas_Gas_Master!$A$1:$Y$167</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -966,30 +969,12 @@
     <t>Galp | Plano Flexível | Gás</t>
   </si>
   <si>
-    <t>Goldenergy  | Digital | Gás | DD+FE</t>
-  </si>
-  <si>
-    <t>Goldenergy  | Digital | Gás | DD ou FE</t>
-  </si>
-  <si>
-    <t>Goldenergy  | Digital | Gás</t>
-  </si>
-  <si>
-    <t>Goldenergy | Gold | Gás</t>
-  </si>
-  <si>
-    <t>Goldenergy | Desconto ao Máximo | Gás</t>
-  </si>
-  <si>
     <t>Galp | Casa &amp; Estrada | Gás | (- 4% 1 energia s/DD)</t>
   </si>
   <si>
     <t>Galp | Casa &amp; Estrada | Gás | (- 6% 1 energia c/DD ou 2 energias s/DD)</t>
   </si>
   <si>
-    <t>Goldenergy | ACP | Gás</t>
-  </si>
-  <si>
     <t>Doméstico e Não Doméstico</t>
   </si>
   <si>
@@ -1120,6 +1105,24 @@
   </si>
   <si>
     <t>EDP | Indexado | Gás</t>
+  </si>
+  <si>
+    <t>Goldenergy | Digital | Gás · (-12%) | DD + FE | Há 10€ desconto Código Amigo</t>
+  </si>
+  <si>
+    <t>Goldenergy | Digital | Gás · (-8,5%) | DD ou FE | Há 10€ desconto Código Amigo</t>
+  </si>
+  <si>
+    <t>Goldenergy | Digital | Gás | Há 10€ desconto Código Amigo</t>
+  </si>
+  <si>
+    <t>Goldenergy | Gold | Gás | Há 10€ desconto Código Amigo</t>
+  </si>
+  <si>
+    <t>Goldenergy | Desconto ao Máximo | Gás | Há 10€ desconto Código Amigo</t>
+  </si>
+  <si>
+    <t>Goldenergy | ACP | Gás | Há 10€ desconto Código Amigo</t>
   </si>
 </sst>
 </file>
@@ -1549,7 +1552,7 @@
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="58.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="70.42578125" customWidth="1"/>
     <col min="3" max="4" width="8.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="24.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="28.85546875" bestFit="1" customWidth="1"/>
@@ -1617,25 +1620,25 @@
         <v>13</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="P1" s="3" t="s">
         <v>14</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="S1" s="3" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="T1" s="3" t="s">
         <v>15</v>
       </c>
       <c r="U1" s="3" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="V1" s="3" t="s">
         <v>16</v>
@@ -1661,7 +1664,7 @@
         <v>19</v>
       </c>
       <c r="E2" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F2" t="s">
         <v>21</v>
@@ -1702,7 +1705,7 @@
         <v>19</v>
       </c>
       <c r="E3" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F3" t="s">
         <v>21</v>
@@ -1743,7 +1746,7 @@
         <v>19</v>
       </c>
       <c r="E4" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F4" t="s">
         <v>21</v>
@@ -1784,7 +1787,7 @@
         <v>19</v>
       </c>
       <c r="E5" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F5" t="s">
         <v>21</v>
@@ -1819,13 +1822,13 @@
         <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="D6" t="s">
         <v>19</v>
       </c>
       <c r="E6" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F6" t="s">
         <v>21</v>
@@ -1852,7 +1855,7 @@
         <v>24</v>
       </c>
       <c r="V6" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.25">
@@ -1860,13 +1863,13 @@
         <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="D7" t="s">
         <v>19</v>
       </c>
       <c r="E7" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F7" t="s">
         <v>21</v>
@@ -1893,7 +1896,7 @@
         <v>24</v>
       </c>
       <c r="V7" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.25">
@@ -1901,13 +1904,13 @@
         <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="D8" t="s">
         <v>19</v>
       </c>
       <c r="E8" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F8" t="s">
         <v>21</v>
@@ -1934,7 +1937,7 @@
         <v>24</v>
       </c>
       <c r="V8" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.25">
@@ -1942,13 +1945,13 @@
         <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="D9" t="s">
         <v>19</v>
       </c>
       <c r="E9" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F9" t="s">
         <v>21</v>
@@ -1975,7 +1978,7 @@
         <v>24</v>
       </c>
       <c r="V9" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.25">
@@ -2803,7 +2806,7 @@
         <v>39</v>
       </c>
       <c r="B30" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="D30" t="s">
         <v>19</v>
@@ -2844,7 +2847,7 @@
         <v>39</v>
       </c>
       <c r="B31" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="D31" t="s">
         <v>19</v>
@@ -2885,7 +2888,7 @@
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="D32" t="s">
         <v>19</v>
@@ -2926,7 +2929,7 @@
         <v>39</v>
       </c>
       <c r="B33" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="D33" t="s">
         <v>19</v>
@@ -2967,7 +2970,7 @@
         <v>39</v>
       </c>
       <c r="B34" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="D34" t="s">
         <v>19</v>
@@ -3008,7 +3011,7 @@
         <v>39</v>
       </c>
       <c r="B35" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="D35" t="s">
         <v>19</v>
@@ -3049,7 +3052,7 @@
         <v>39</v>
       </c>
       <c r="B36" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="D36" t="s">
         <v>19</v>
@@ -3090,7 +3093,7 @@
         <v>39</v>
       </c>
       <c r="B37" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="D37" t="s">
         <v>19</v>
@@ -3131,7 +3134,7 @@
         <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="D38" t="s">
         <v>19</v>
@@ -3172,7 +3175,7 @@
         <v>39</v>
       </c>
       <c r="B39" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="D39" t="s">
         <v>19</v>
@@ -3213,7 +3216,7 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="D40" t="s">
         <v>19</v>
@@ -3254,7 +3257,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="D41" t="s">
         <v>19</v>
@@ -3295,13 +3298,13 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="D42" t="s">
         <v>19</v>
       </c>
       <c r="E42" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="F42" t="s">
         <v>21</v>
@@ -3328,7 +3331,7 @@
         <v>24</v>
       </c>
       <c r="T42" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.25">
@@ -3336,13 +3339,13 @@
         <v>39</v>
       </c>
       <c r="B43" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="D43" t="s">
         <v>19</v>
       </c>
       <c r="E43" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="F43" t="s">
         <v>21</v>
@@ -3369,7 +3372,7 @@
         <v>24</v>
       </c>
       <c r="T43" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.25">
@@ -3377,13 +3380,13 @@
         <v>39</v>
       </c>
       <c r="B44" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="D44" t="s">
         <v>19</v>
       </c>
       <c r="E44" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="F44" t="s">
         <v>21</v>
@@ -3410,7 +3413,7 @@
         <v>24</v>
       </c>
       <c r="T44" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.25">
@@ -3418,13 +3421,13 @@
         <v>39</v>
       </c>
       <c r="B45" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="D45" t="s">
         <v>19</v>
       </c>
       <c r="E45" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="F45" t="s">
         <v>21</v>
@@ -3451,7 +3454,7 @@
         <v>24</v>
       </c>
       <c r="T45" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
     </row>
     <row r="46" spans="1:20" x14ac:dyDescent="0.25">
@@ -3459,7 +3462,7 @@
         <v>39</v>
       </c>
       <c r="B46" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="D46" t="s">
         <v>41</v>
@@ -3500,7 +3503,7 @@
         <v>39</v>
       </c>
       <c r="B47" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="D47" t="s">
         <v>41</v>
@@ -3541,7 +3544,7 @@
         <v>39</v>
       </c>
       <c r="B48" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="D48" t="s">
         <v>41</v>
@@ -3582,7 +3585,7 @@
         <v>39</v>
       </c>
       <c r="B49" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="D49" t="s">
         <v>41</v>
@@ -3623,13 +3626,13 @@
         <v>45</v>
       </c>
       <c r="B50" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="D50" t="s">
         <v>19</v>
       </c>
       <c r="E50" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F50" t="s">
         <v>34</v>
@@ -3662,7 +3665,7 @@
         <v>46</v>
       </c>
       <c r="V50" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
     </row>
     <row r="51" spans="1:25" x14ac:dyDescent="0.25">
@@ -3670,13 +3673,13 @@
         <v>45</v>
       </c>
       <c r="B51" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="D51" t="s">
         <v>19</v>
       </c>
       <c r="E51" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F51" t="s">
         <v>34</v>
@@ -3709,7 +3712,7 @@
         <v>46</v>
       </c>
       <c r="V51" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
     </row>
     <row r="52" spans="1:25" x14ac:dyDescent="0.25">
@@ -3717,13 +3720,13 @@
         <v>45</v>
       </c>
       <c r="B52" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="D52" t="s">
         <v>19</v>
       </c>
       <c r="E52" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F52" t="s">
         <v>34</v>
@@ -3756,7 +3759,7 @@
         <v>46</v>
       </c>
       <c r="V52" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
     </row>
     <row r="53" spans="1:25" x14ac:dyDescent="0.25">
@@ -3764,13 +3767,13 @@
         <v>45</v>
       </c>
       <c r="B53" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="D53" t="s">
         <v>19</v>
       </c>
       <c r="E53" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F53" t="s">
         <v>34</v>
@@ -3803,7 +3806,7 @@
         <v>46</v>
       </c>
       <c r="V53" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
     </row>
     <row r="54" spans="1:25" x14ac:dyDescent="0.25">
@@ -3811,13 +3814,13 @@
         <v>45</v>
       </c>
       <c r="B54" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="D54" t="s">
         <v>19</v>
       </c>
       <c r="E54" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F54" t="s">
         <v>34</v>
@@ -3856,13 +3859,13 @@
         <v>47</v>
       </c>
       <c r="V54" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="W54">
         <v>3</v>
       </c>
       <c r="X54" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
     </row>
     <row r="55" spans="1:25" x14ac:dyDescent="0.25">
@@ -3870,13 +3873,13 @@
         <v>45</v>
       </c>
       <c r="B55" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="D55" t="s">
         <v>19</v>
       </c>
       <c r="E55" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F55" t="s">
         <v>34</v>
@@ -3915,13 +3918,13 @@
         <v>47</v>
       </c>
       <c r="V55" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="W55">
         <v>3</v>
       </c>
       <c r="X55" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
     </row>
     <row r="56" spans="1:25" x14ac:dyDescent="0.25">
@@ -3929,13 +3932,13 @@
         <v>45</v>
       </c>
       <c r="B56" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="D56" t="s">
         <v>19</v>
       </c>
       <c r="E56" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F56" t="s">
         <v>34</v>
@@ -3974,13 +3977,13 @@
         <v>47</v>
       </c>
       <c r="V56" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="W56">
         <v>3</v>
       </c>
       <c r="X56" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
     </row>
     <row r="57" spans="1:25" x14ac:dyDescent="0.25">
@@ -3988,13 +3991,13 @@
         <v>45</v>
       </c>
       <c r="B57" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="D57" t="s">
         <v>19</v>
       </c>
       <c r="E57" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F57" t="s">
         <v>34</v>
@@ -4033,13 +4036,13 @@
         <v>47</v>
       </c>
       <c r="V57" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="W57">
         <v>3</v>
       </c>
       <c r="X57" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
     </row>
     <row r="58" spans="1:25" x14ac:dyDescent="0.25">
@@ -4047,13 +4050,13 @@
         <v>45</v>
       </c>
       <c r="B58" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="D58" t="s">
         <v>19</v>
       </c>
       <c r="E58" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F58" t="s">
         <v>34</v>
@@ -4092,7 +4095,7 @@
         <v>47</v>
       </c>
       <c r="V58" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="Y58">
         <v>1</v>
@@ -4103,13 +4106,13 @@
         <v>45</v>
       </c>
       <c r="B59" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="D59" t="s">
         <v>19</v>
       </c>
       <c r="E59" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F59" t="s">
         <v>34</v>
@@ -4148,7 +4151,7 @@
         <v>47</v>
       </c>
       <c r="V59" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="Y59">
         <v>1</v>
@@ -4159,13 +4162,13 @@
         <v>45</v>
       </c>
       <c r="B60" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="D60" t="s">
         <v>19</v>
       </c>
       <c r="E60" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F60" t="s">
         <v>34</v>
@@ -4204,7 +4207,7 @@
         <v>47</v>
       </c>
       <c r="V60" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="Y60">
         <v>1</v>
@@ -4215,13 +4218,13 @@
         <v>45</v>
       </c>
       <c r="B61" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="D61" t="s">
         <v>19</v>
       </c>
       <c r="E61" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F61" t="s">
         <v>34</v>
@@ -4260,7 +4263,7 @@
         <v>47</v>
       </c>
       <c r="V61" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="Y61">
         <v>1</v>
@@ -4271,13 +4274,13 @@
         <v>45</v>
       </c>
       <c r="B62" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="D62" t="s">
         <v>19</v>
       </c>
       <c r="E62" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F62" t="s">
         <v>21</v>
@@ -4316,13 +4319,13 @@
         <v>47</v>
       </c>
       <c r="V62" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="W62">
         <v>3</v>
       </c>
       <c r="X62" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
     </row>
     <row r="63" spans="1:25" x14ac:dyDescent="0.25">
@@ -4330,13 +4333,13 @@
         <v>45</v>
       </c>
       <c r="B63" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="D63" t="s">
         <v>19</v>
       </c>
       <c r="E63" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F63" t="s">
         <v>21</v>
@@ -4375,13 +4378,13 @@
         <v>47</v>
       </c>
       <c r="V63" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="W63">
         <v>3</v>
       </c>
       <c r="X63" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
     </row>
     <row r="64" spans="1:25" x14ac:dyDescent="0.25">
@@ -4389,13 +4392,13 @@
         <v>45</v>
       </c>
       <c r="B64" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="D64" t="s">
         <v>19</v>
       </c>
       <c r="E64" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F64" t="s">
         <v>21</v>
@@ -4434,13 +4437,13 @@
         <v>47</v>
       </c>
       <c r="V64" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="W64">
         <v>3</v>
       </c>
       <c r="X64" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
     </row>
     <row r="65" spans="1:25" x14ac:dyDescent="0.25">
@@ -4448,13 +4451,13 @@
         <v>45</v>
       </c>
       <c r="B65" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="D65" t="s">
         <v>19</v>
       </c>
       <c r="E65" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F65" t="s">
         <v>21</v>
@@ -4493,13 +4496,13 @@
         <v>47</v>
       </c>
       <c r="V65" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="W65">
         <v>3</v>
       </c>
       <c r="X65" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
     </row>
     <row r="66" spans="1:25" x14ac:dyDescent="0.25">
@@ -4507,13 +4510,13 @@
         <v>45</v>
       </c>
       <c r="B66" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="D66" t="s">
         <v>19</v>
       </c>
       <c r="E66" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F66" t="s">
         <v>21</v>
@@ -4552,7 +4555,7 @@
         <v>47</v>
       </c>
       <c r="V66" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="Y66">
         <v>1</v>
@@ -4563,13 +4566,13 @@
         <v>45</v>
       </c>
       <c r="B67" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="D67" t="s">
         <v>19</v>
       </c>
       <c r="E67" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F67" t="s">
         <v>21</v>
@@ -4608,7 +4611,7 @@
         <v>47</v>
       </c>
       <c r="V67" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="Y67">
         <v>1</v>
@@ -4619,13 +4622,13 @@
         <v>45</v>
       </c>
       <c r="B68" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="D68" t="s">
         <v>19</v>
       </c>
       <c r="E68" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F68" t="s">
         <v>21</v>
@@ -4664,7 +4667,7 @@
         <v>47</v>
       </c>
       <c r="V68" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="Y68">
         <v>1</v>
@@ -4675,13 +4678,13 @@
         <v>45</v>
       </c>
       <c r="B69" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="D69" t="s">
         <v>19</v>
       </c>
       <c r="E69" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F69" t="s">
         <v>21</v>
@@ -4720,7 +4723,7 @@
         <v>47</v>
       </c>
       <c r="V69" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="Y69">
         <v>1</v>
@@ -4731,13 +4734,13 @@
         <v>45</v>
       </c>
       <c r="B70" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="D70" t="s">
         <v>19</v>
       </c>
       <c r="E70" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F70" t="s">
         <v>34</v>
@@ -4767,7 +4770,7 @@
         <v>1.23</v>
       </c>
       <c r="T70" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
     </row>
     <row r="71" spans="1:25" x14ac:dyDescent="0.25">
@@ -4775,13 +4778,13 @@
         <v>45</v>
       </c>
       <c r="B71" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="D71" t="s">
         <v>19</v>
       </c>
       <c r="E71" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F71" t="s">
         <v>34</v>
@@ -4811,7 +4814,7 @@
         <v>1.23</v>
       </c>
       <c r="T71" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
     </row>
     <row r="72" spans="1:25" x14ac:dyDescent="0.25">
@@ -4819,13 +4822,13 @@
         <v>45</v>
       </c>
       <c r="B72" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="D72" t="s">
         <v>41</v>
       </c>
       <c r="E72" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F72" t="s">
         <v>21</v>
@@ -4863,13 +4866,13 @@
         <v>45</v>
       </c>
       <c r="B73" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="D73" t="s">
         <v>41</v>
       </c>
       <c r="E73" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F73" t="s">
         <v>21</v>
@@ -4907,13 +4910,13 @@
         <v>45</v>
       </c>
       <c r="B74" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="D74" t="s">
         <v>41</v>
       </c>
       <c r="E74" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F74" t="s">
         <v>21</v>
@@ -4951,13 +4954,13 @@
         <v>45</v>
       </c>
       <c r="B75" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="D75" t="s">
         <v>41</v>
       </c>
       <c r="E75" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F75" t="s">
         <v>21</v>
@@ -4995,13 +4998,13 @@
         <v>45</v>
       </c>
       <c r="B76" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="D76" t="s">
         <v>19</v>
       </c>
       <c r="E76" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F76" t="s">
         <v>21</v>
@@ -5034,7 +5037,7 @@
         <v>49</v>
       </c>
       <c r="V76" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
     </row>
     <row r="77" spans="1:25" x14ac:dyDescent="0.25">
@@ -5042,13 +5045,13 @@
         <v>45</v>
       </c>
       <c r="B77" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="D77" t="s">
         <v>19</v>
       </c>
       <c r="E77" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F77" t="s">
         <v>21</v>
@@ -5081,7 +5084,7 @@
         <v>49</v>
       </c>
       <c r="V77" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
     </row>
     <row r="78" spans="1:25" x14ac:dyDescent="0.25">
@@ -5089,13 +5092,13 @@
         <v>45</v>
       </c>
       <c r="B78" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="D78" t="s">
         <v>19</v>
       </c>
       <c r="E78" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F78" t="s">
         <v>21</v>
@@ -5128,7 +5131,7 @@
         <v>49</v>
       </c>
       <c r="V78" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
     </row>
     <row r="79" spans="1:25" x14ac:dyDescent="0.25">
@@ -5136,13 +5139,13 @@
         <v>45</v>
       </c>
       <c r="B79" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="D79" t="s">
         <v>19</v>
       </c>
       <c r="E79" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F79" t="s">
         <v>21</v>
@@ -5175,7 +5178,7 @@
         <v>49</v>
       </c>
       <c r="V79" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
     </row>
     <row r="80" spans="1:25" x14ac:dyDescent="0.25">
@@ -5183,7 +5186,7 @@
         <v>50</v>
       </c>
       <c r="B80" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="D80" t="s">
         <v>19</v>
@@ -5225,7 +5228,7 @@
         <v>50</v>
       </c>
       <c r="B81" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="D81" t="s">
         <v>19</v>
@@ -5267,7 +5270,7 @@
         <v>50</v>
       </c>
       <c r="B82" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="D82" t="s">
         <v>19</v>
@@ -5309,7 +5312,7 @@
         <v>50</v>
       </c>
       <c r="B83" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="D83" t="s">
         <v>19</v>
@@ -5351,7 +5354,7 @@
         <v>50</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="D84" t="s">
         <v>19</v>
@@ -5392,7 +5395,7 @@
         <v>50</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="D85" t="s">
         <v>19</v>
@@ -5433,7 +5436,7 @@
         <v>50</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="D86" t="s">
         <v>19</v>
@@ -5474,7 +5477,7 @@
         <v>50</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="D87" t="s">
         <v>19</v>
@@ -5515,7 +5518,7 @@
         <v>50</v>
       </c>
       <c r="B88" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="D88" t="s">
         <v>19</v>
@@ -5556,7 +5559,7 @@
         <v>50</v>
       </c>
       <c r="B89" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="D89" t="s">
         <v>19</v>
@@ -5597,7 +5600,7 @@
         <v>50</v>
       </c>
       <c r="B90" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="D90" t="s">
         <v>19</v>
@@ -5638,7 +5641,7 @@
         <v>50</v>
       </c>
       <c r="B91" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="D91" t="s">
         <v>19</v>
@@ -5843,13 +5846,13 @@
         <v>50</v>
       </c>
       <c r="B96" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="D96" t="s">
         <v>19</v>
       </c>
       <c r="E96" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="F96" t="s">
         <v>21</v>
@@ -5876,7 +5879,7 @@
         <v>24</v>
       </c>
       <c r="T96" s="4" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="U96" s="4"/>
     </row>
@@ -5885,13 +5888,13 @@
         <v>50</v>
       </c>
       <c r="B97" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="D97" t="s">
         <v>19</v>
       </c>
       <c r="E97" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="F97" t="s">
         <v>21</v>
@@ -5918,7 +5921,7 @@
         <v>24</v>
       </c>
       <c r="T97" s="4" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="U97" s="4"/>
     </row>
@@ -5927,13 +5930,13 @@
         <v>50</v>
       </c>
       <c r="B98" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="D98" t="s">
         <v>19</v>
       </c>
       <c r="E98" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="F98" t="s">
         <v>21</v>
@@ -5960,7 +5963,7 @@
         <v>24</v>
       </c>
       <c r="T98" s="4" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="U98" s="4"/>
     </row>
@@ -5969,13 +5972,13 @@
         <v>50</v>
       </c>
       <c r="B99" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="D99" t="s">
         <v>19</v>
       </c>
       <c r="E99" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="F99" t="s">
         <v>21</v>
@@ -6002,7 +6005,7 @@
         <v>24</v>
       </c>
       <c r="T99" s="4" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="U99" s="4"/>
     </row>
@@ -6011,13 +6014,13 @@
         <v>50</v>
       </c>
       <c r="B100" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="D100" t="s">
         <v>19</v>
       </c>
       <c r="E100" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="F100" t="s">
         <v>21</v>
@@ -6044,7 +6047,7 @@
         <v>24</v>
       </c>
       <c r="T100" s="4" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="U100" s="4"/>
     </row>
@@ -6053,13 +6056,13 @@
         <v>50</v>
       </c>
       <c r="B101" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="D101" t="s">
         <v>19</v>
       </c>
       <c r="E101" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="F101" t="s">
         <v>21</v>
@@ -6086,7 +6089,7 @@
         <v>24</v>
       </c>
       <c r="T101" s="4" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="U101" s="4"/>
     </row>
@@ -6095,13 +6098,13 @@
         <v>50</v>
       </c>
       <c r="B102" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="D102" t="s">
         <v>19</v>
       </c>
       <c r="E102" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="F102" t="s">
         <v>21</v>
@@ -6128,7 +6131,7 @@
         <v>24</v>
       </c>
       <c r="T102" s="4" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="U102" s="4"/>
     </row>
@@ -6137,13 +6140,13 @@
         <v>50</v>
       </c>
       <c r="B103" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="D103" t="s">
         <v>19</v>
       </c>
       <c r="E103" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="F103" t="s">
         <v>21</v>
@@ -6170,7 +6173,7 @@
         <v>24</v>
       </c>
       <c r="T103" s="4" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="U103" s="4"/>
     </row>
@@ -6179,13 +6182,13 @@
         <v>54</v>
       </c>
       <c r="B104" t="s">
-        <v>316</v>
+        <v>360</v>
       </c>
       <c r="D104" t="s">
         <v>19</v>
       </c>
       <c r="E104" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F104" t="s">
         <v>21</v>
@@ -6220,13 +6223,13 @@
         <v>54</v>
       </c>
       <c r="B105" t="s">
-        <v>316</v>
+        <v>360</v>
       </c>
       <c r="D105" t="s">
         <v>19</v>
       </c>
       <c r="E105" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F105" t="s">
         <v>21</v>
@@ -6261,13 +6264,13 @@
         <v>54</v>
       </c>
       <c r="B106" t="s">
-        <v>316</v>
+        <v>360</v>
       </c>
       <c r="D106" t="s">
         <v>19</v>
       </c>
       <c r="E106" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F106" t="s">
         <v>21</v>
@@ -6302,13 +6305,13 @@
         <v>54</v>
       </c>
       <c r="B107" t="s">
-        <v>316</v>
+        <v>360</v>
       </c>
       <c r="D107" t="s">
         <v>19</v>
       </c>
       <c r="E107" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F107" t="s">
         <v>21</v>
@@ -6343,13 +6346,13 @@
         <v>54</v>
       </c>
       <c r="B108" t="s">
-        <v>309</v>
+        <v>355</v>
       </c>
       <c r="D108" t="s">
         <v>19</v>
       </c>
       <c r="E108" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F108" t="s">
         <v>34</v>
@@ -6384,13 +6387,13 @@
         <v>54</v>
       </c>
       <c r="B109" t="s">
-        <v>309</v>
+        <v>355</v>
       </c>
       <c r="D109" t="s">
         <v>19</v>
       </c>
       <c r="E109" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F109" t="s">
         <v>34</v>
@@ -6425,13 +6428,13 @@
         <v>54</v>
       </c>
       <c r="B110" t="s">
-        <v>309</v>
+        <v>355</v>
       </c>
       <c r="D110" t="s">
         <v>19</v>
       </c>
       <c r="E110" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F110" t="s">
         <v>34</v>
@@ -6466,13 +6469,13 @@
         <v>54</v>
       </c>
       <c r="B111" t="s">
-        <v>309</v>
+        <v>355</v>
       </c>
       <c r="D111" t="s">
         <v>19</v>
       </c>
       <c r="E111" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F111" t="s">
         <v>34</v>
@@ -6507,13 +6510,13 @@
         <v>54</v>
       </c>
       <c r="B112" t="s">
-        <v>310</v>
+        <v>356</v>
       </c>
       <c r="D112" t="s">
         <v>19</v>
       </c>
       <c r="E112" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F112" t="s">
         <v>21</v>
@@ -6548,13 +6551,13 @@
         <v>54</v>
       </c>
       <c r="B113" t="s">
-        <v>310</v>
+        <v>356</v>
       </c>
       <c r="D113" t="s">
         <v>19</v>
       </c>
       <c r="E113" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F113" t="s">
         <v>21</v>
@@ -6589,13 +6592,13 @@
         <v>54</v>
       </c>
       <c r="B114" t="s">
-        <v>310</v>
+        <v>356</v>
       </c>
       <c r="D114" t="s">
         <v>19</v>
       </c>
       <c r="E114" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F114" t="s">
         <v>21</v>
@@ -6630,13 +6633,13 @@
         <v>54</v>
       </c>
       <c r="B115" t="s">
-        <v>310</v>
+        <v>356</v>
       </c>
       <c r="D115" t="s">
         <v>19</v>
       </c>
       <c r="E115" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F115" t="s">
         <v>21</v>
@@ -6671,13 +6674,13 @@
         <v>54</v>
       </c>
       <c r="B116" t="s">
-        <v>311</v>
+        <v>357</v>
       </c>
       <c r="D116" t="s">
         <v>19</v>
       </c>
       <c r="E116" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F116" t="s">
         <v>21</v>
@@ -6712,13 +6715,13 @@
         <v>54</v>
       </c>
       <c r="B117" t="s">
-        <v>311</v>
+        <v>357</v>
       </c>
       <c r="D117" t="s">
         <v>19</v>
       </c>
       <c r="E117" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F117" t="s">
         <v>21</v>
@@ -6753,13 +6756,13 @@
         <v>54</v>
       </c>
       <c r="B118" t="s">
-        <v>311</v>
+        <v>357</v>
       </c>
       <c r="D118" t="s">
         <v>19</v>
       </c>
       <c r="E118" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F118" t="s">
         <v>21</v>
@@ -6794,13 +6797,13 @@
         <v>54</v>
       </c>
       <c r="B119" t="s">
-        <v>311</v>
+        <v>357</v>
       </c>
       <c r="D119" t="s">
         <v>19</v>
       </c>
       <c r="E119" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F119" t="s">
         <v>21</v>
@@ -6835,13 +6838,13 @@
         <v>54</v>
       </c>
       <c r="B120" t="s">
-        <v>312</v>
+        <v>358</v>
       </c>
       <c r="D120" t="s">
         <v>19</v>
       </c>
       <c r="E120" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F120" t="s">
         <v>21</v>
@@ -6876,13 +6879,13 @@
         <v>54</v>
       </c>
       <c r="B121" t="s">
-        <v>312</v>
+        <v>358</v>
       </c>
       <c r="D121" t="s">
         <v>19</v>
       </c>
       <c r="E121" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F121" t="s">
         <v>21</v>
@@ -6917,13 +6920,13 @@
         <v>54</v>
       </c>
       <c r="B122" t="s">
-        <v>312</v>
+        <v>358</v>
       </c>
       <c r="D122" t="s">
         <v>19</v>
       </c>
       <c r="E122" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F122" t="s">
         <v>21</v>
@@ -6958,13 +6961,13 @@
         <v>54</v>
       </c>
       <c r="B123" t="s">
-        <v>312</v>
+        <v>358</v>
       </c>
       <c r="D123" t="s">
         <v>19</v>
       </c>
       <c r="E123" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F123" t="s">
         <v>21</v>
@@ -6999,13 +7002,13 @@
         <v>54</v>
       </c>
       <c r="B124" t="s">
-        <v>313</v>
+        <v>359</v>
       </c>
       <c r="D124" t="s">
         <v>19</v>
       </c>
       <c r="E124" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F124" t="s">
         <v>21</v>
@@ -7040,13 +7043,13 @@
         <v>54</v>
       </c>
       <c r="B125" t="s">
-        <v>313</v>
+        <v>359</v>
       </c>
       <c r="D125" t="s">
         <v>19</v>
       </c>
       <c r="E125" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F125" t="s">
         <v>21</v>
@@ -7081,13 +7084,13 @@
         <v>54</v>
       </c>
       <c r="B126" t="s">
-        <v>313</v>
+        <v>359</v>
       </c>
       <c r="D126" t="s">
         <v>19</v>
       </c>
       <c r="E126" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F126" t="s">
         <v>21</v>
@@ -7122,13 +7125,13 @@
         <v>54</v>
       </c>
       <c r="B127" t="s">
-        <v>313</v>
+        <v>359</v>
       </c>
       <c r="D127" t="s">
         <v>19</v>
       </c>
       <c r="E127" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F127" t="s">
         <v>21</v>
@@ -7169,7 +7172,7 @@
         <v>41</v>
       </c>
       <c r="E128" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F128" t="s">
         <v>21</v>
@@ -7210,7 +7213,7 @@
         <v>41</v>
       </c>
       <c r="E129" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F129" t="s">
         <v>21</v>
@@ -7251,7 +7254,7 @@
         <v>41</v>
       </c>
       <c r="E130" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F130" t="s">
         <v>21</v>
@@ -7292,7 +7295,7 @@
         <v>41</v>
       </c>
       <c r="E131" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F131" t="s">
         <v>21</v>
@@ -7327,7 +7330,7 @@
         <v>56</v>
       </c>
       <c r="B132" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="D132" t="s">
         <v>19</v>
@@ -7368,7 +7371,7 @@
         <v>56</v>
       </c>
       <c r="B133" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="D133" t="s">
         <v>19</v>
@@ -7409,7 +7412,7 @@
         <v>56</v>
       </c>
       <c r="B134" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="D134" t="s">
         <v>19</v>
@@ -7450,7 +7453,7 @@
         <v>56</v>
       </c>
       <c r="B135" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="D135" t="s">
         <v>19</v>
@@ -7491,7 +7494,7 @@
         <v>56</v>
       </c>
       <c r="B136" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="D136" t="s">
         <v>19</v>
@@ -7532,7 +7535,7 @@
         <v>56</v>
       </c>
       <c r="B137" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="D137" t="s">
         <v>19</v>
@@ -7573,7 +7576,7 @@
         <v>56</v>
       </c>
       <c r="B138" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="D138" t="s">
         <v>19</v>
@@ -7614,7 +7617,7 @@
         <v>56</v>
       </c>
       <c r="B139" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="D139" t="s">
         <v>19</v>
@@ -7655,7 +7658,7 @@
         <v>56</v>
       </c>
       <c r="B140" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="D140" t="s">
         <v>19</v>
@@ -7696,7 +7699,7 @@
         <v>56</v>
       </c>
       <c r="B141" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="D141" t="s">
         <v>19</v>
@@ -7737,7 +7740,7 @@
         <v>56</v>
       </c>
       <c r="B142" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="D142" t="s">
         <v>19</v>
@@ -7778,7 +7781,7 @@
         <v>56</v>
       </c>
       <c r="B143" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="D143" t="s">
         <v>19</v>
@@ -7819,13 +7822,13 @@
         <v>56</v>
       </c>
       <c r="B144" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="D144" t="s">
         <v>19</v>
       </c>
       <c r="E144" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="F144" t="s">
         <v>21</v>
@@ -7852,7 +7855,7 @@
         <v>24</v>
       </c>
       <c r="T144" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
     </row>
     <row r="145" spans="1:20" x14ac:dyDescent="0.25">
@@ -7860,13 +7863,13 @@
         <v>56</v>
       </c>
       <c r="B145" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="D145" t="s">
         <v>19</v>
       </c>
       <c r="E145" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="F145" t="s">
         <v>21</v>
@@ -7893,7 +7896,7 @@
         <v>24</v>
       </c>
       <c r="T145" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
     </row>
     <row r="146" spans="1:20" x14ac:dyDescent="0.25">
@@ -7901,13 +7904,13 @@
         <v>56</v>
       </c>
       <c r="B146" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="D146" t="s">
         <v>19</v>
       </c>
       <c r="E146" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="F146" t="s">
         <v>21</v>
@@ -7934,7 +7937,7 @@
         <v>24</v>
       </c>
       <c r="T146" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
     </row>
     <row r="147" spans="1:20" x14ac:dyDescent="0.25">
@@ -7942,13 +7945,13 @@
         <v>56</v>
       </c>
       <c r="B147" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="D147" t="s">
         <v>19</v>
       </c>
       <c r="E147" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="F147" t="s">
         <v>21</v>
@@ -7975,7 +7978,7 @@
         <v>24</v>
       </c>
       <c r="T147" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
     </row>
     <row r="148" spans="1:20" x14ac:dyDescent="0.25">
@@ -7983,13 +7986,13 @@
         <v>56</v>
       </c>
       <c r="B148" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="D148" t="s">
         <v>19</v>
       </c>
       <c r="E148" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="F148" t="s">
         <v>21</v>
@@ -8016,7 +8019,7 @@
         <v>24</v>
       </c>
       <c r="T148" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
     </row>
     <row r="149" spans="1:20" x14ac:dyDescent="0.25">
@@ -8024,13 +8027,13 @@
         <v>56</v>
       </c>
       <c r="B149" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="D149" t="s">
         <v>19</v>
       </c>
       <c r="E149" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="F149" t="s">
         <v>21</v>
@@ -8057,7 +8060,7 @@
         <v>24</v>
       </c>
       <c r="T149" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
     </row>
     <row r="150" spans="1:20" x14ac:dyDescent="0.25">
@@ -8065,13 +8068,13 @@
         <v>56</v>
       </c>
       <c r="B150" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="D150" t="s">
         <v>19</v>
       </c>
       <c r="E150" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="F150" t="s">
         <v>21</v>
@@ -8098,7 +8101,7 @@
         <v>24</v>
       </c>
       <c r="T150" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
     </row>
     <row r="151" spans="1:20" x14ac:dyDescent="0.25">
@@ -8106,13 +8109,13 @@
         <v>56</v>
       </c>
       <c r="B151" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="D151" t="s">
         <v>19</v>
       </c>
       <c r="E151" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="F151" t="s">
         <v>21</v>
@@ -8139,7 +8142,7 @@
         <v>24</v>
       </c>
       <c r="T151" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
     </row>
     <row r="152" spans="1:20" x14ac:dyDescent="0.25">
@@ -8147,13 +8150,13 @@
         <v>56</v>
       </c>
       <c r="B152" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="D152" t="s">
         <v>19</v>
       </c>
       <c r="E152" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="F152" t="s">
         <v>34</v>
@@ -8180,7 +8183,7 @@
         <v>24</v>
       </c>
       <c r="T152" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
     </row>
     <row r="153" spans="1:20" x14ac:dyDescent="0.25">
@@ -8188,13 +8191,13 @@
         <v>56</v>
       </c>
       <c r="B153" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="D153" t="s">
         <v>19</v>
       </c>
       <c r="E153" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="F153" t="s">
         <v>34</v>
@@ -8221,7 +8224,7 @@
         <v>24</v>
       </c>
       <c r="T153" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
     </row>
     <row r="154" spans="1:20" x14ac:dyDescent="0.25">
@@ -8229,13 +8232,13 @@
         <v>56</v>
       </c>
       <c r="B154" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="D154" t="s">
         <v>19</v>
       </c>
       <c r="E154" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="F154" t="s">
         <v>34</v>
@@ -8262,7 +8265,7 @@
         <v>24</v>
       </c>
       <c r="T154" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
     </row>
     <row r="155" spans="1:20" x14ac:dyDescent="0.25">
@@ -8270,13 +8273,13 @@
         <v>56</v>
       </c>
       <c r="B155" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="D155" t="s">
         <v>19</v>
       </c>
       <c r="E155" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="F155" t="s">
         <v>34</v>
@@ -8303,7 +8306,7 @@
         <v>24</v>
       </c>
       <c r="T155" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
     </row>
     <row r="156" spans="1:20" x14ac:dyDescent="0.25">
@@ -8317,7 +8320,7 @@
         <v>19</v>
       </c>
       <c r="E156" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F156" t="s">
         <v>21</v>
@@ -8358,7 +8361,7 @@
         <v>19</v>
       </c>
       <c r="E157" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F157" t="s">
         <v>21</v>
@@ -8399,7 +8402,7 @@
         <v>19</v>
       </c>
       <c r="E158" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F158" t="s">
         <v>21</v>
@@ -8440,7 +8443,7 @@
         <v>19</v>
       </c>
       <c r="E159" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F159" t="s">
         <v>21</v>
@@ -8481,7 +8484,7 @@
         <v>41</v>
       </c>
       <c r="E160" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F160" t="s">
         <v>21</v>
@@ -8522,7 +8525,7 @@
         <v>41</v>
       </c>
       <c r="E161" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F161" t="s">
         <v>21</v>
@@ -8563,7 +8566,7 @@
         <v>41</v>
       </c>
       <c r="E162" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F162" t="s">
         <v>21</v>
@@ -8604,7 +8607,7 @@
         <v>41</v>
       </c>
       <c r="E163" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F163" t="s">
         <v>21</v>
@@ -8645,7 +8648,7 @@
         <v>19</v>
       </c>
       <c r="E164" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F164" t="s">
         <v>21</v>
@@ -8686,7 +8689,7 @@
         <v>19</v>
       </c>
       <c r="E165" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F165" t="s">
         <v>21</v>
@@ -8727,7 +8730,7 @@
         <v>19</v>
       </c>
       <c r="E166" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F166" t="s">
         <v>21</v>
@@ -8768,7 +8771,7 @@
         <v>19</v>
       </c>
       <c r="E167" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F167" t="s">
         <v>21</v>
@@ -8799,6 +8802,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:Y167" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
